--- a/inst/extdata/southern_ute_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/southern_ute_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/k_salkgundersen_tetratech_com/Documents/EPA/R8_AssessmentTool/5_Work/Crosswalks/individual_criteria_crosswalks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4185BC0D-2CF8-4FCA-B329-9EC370E2672A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D29BD9-C78F-4910-81E6-3B904012C5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8519E9F5-E322-41EB-A2D9-94E5D3901206}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8519E9F5-E322-41EB-A2D9-94E5D3901206}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="148">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -215,9 +215,6 @@
     <t>Warm water</t>
   </si>
   <si>
-    <t>Oxygen</t>
-  </si>
-  <si>
     <t>DISSOLVED OXYGEN (DO)</t>
   </si>
   <si>
@@ -263,9 +260,6 @@
     <t>(e^(0.7977*[ln(hardness)]-3.909))*1.101672 -[(ln hardness) * (0.041838)]</t>
   </si>
   <si>
-    <t>Chromium III</t>
-  </si>
-  <si>
     <t>CHROMIUM(III)</t>
   </si>
   <si>
@@ -380,9 +374,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Chromium (VI)</t>
-  </si>
-  <si>
     <t>CHROMIUM(VI)</t>
   </si>
   <si>
@@ -461,9 +452,6 @@
     <t>MANGANESE</t>
   </si>
   <si>
-    <t>Methyl Mercury</t>
-  </si>
-  <si>
     <t>DIMETHYLMERCURY</t>
   </si>
   <si>
@@ -473,16 +461,25 @@
     <t>METHYLMERCURY(1+)</t>
   </si>
   <si>
-    <t>Nitrates</t>
-  </si>
-  <si>
     <t>NITRATE</t>
   </si>
   <si>
-    <t>Dissolved Solids</t>
-  </si>
-  <si>
     <t>TOTAL DISSOLVED SOLIDS</t>
+  </si>
+  <si>
+    <t>DISSOLVED OXYGEN</t>
+  </si>
+  <si>
+    <t>CHROMIUM, TRIVALENT, TOTAL</t>
+  </si>
+  <si>
+    <t>CHROMIUM, HEXAVALENT</t>
+  </si>
+  <si>
+    <t>METHYLMERCURY</t>
+  </si>
+  <si>
+    <t>TOTAL DISSOLVED SOLIDS (TDS)</t>
   </si>
 </sst>
 </file>
@@ -892,9 +889,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C89350-85A2-44F8-BF86-837CAD77A8FE}">
   <dimension ref="A1:AQ62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:43" s="4" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" s="4" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1025,7 +1022,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
       <c r="B2" s="5" t="s">
         <v>43</v>
@@ -1094,7 +1091,7 @@
       <c r="AL2" s="5"/>
       <c r="AM2" s="5"/>
     </row>
-    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
         <v>43</v>
@@ -1165,7 +1162,7 @@
       <c r="AL3" s="5"/>
       <c r="AM3" s="5"/>
     </row>
-    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
         <v>43</v>
@@ -1234,7 +1231,7 @@
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
     </row>
-    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
         <v>43</v>
@@ -1305,7 +1302,7 @@
       <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
     </row>
-    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>43</v>
@@ -1374,7 +1371,7 @@
       <c r="AL6" s="5"/>
       <c r="AM6" s="5"/>
     </row>
-    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
         <v>43</v>
@@ -1445,22 +1442,22 @@
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
     </row>
-    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="B8" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
@@ -1480,22 +1477,22 @@
       </c>
       <c r="O8" s="5"/>
       <c r="P8" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>1</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="S8" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="Q8" s="5">
-        <v>1</v>
-      </c>
-      <c r="R8" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="S8" s="5" t="s">
+      <c r="T8" s="5">
+        <v>1</v>
+      </c>
+      <c r="U8" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="T8" s="5">
-        <v>1</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="V8" s="5"/>
       <c r="W8" s="5"/>
@@ -1516,22 +1513,22 @@
       <c r="AL8" s="5"/>
       <c r="AM8" s="5"/>
     </row>
-    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
       <c r="B9" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -1551,22 +1548,22 @@
       </c>
       <c r="O9" s="5"/>
       <c r="P9" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>1</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="S9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="Q9" s="5">
-        <v>1</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="S9" s="5" t="s">
+      <c r="T9" s="5">
+        <v>1</v>
+      </c>
+      <c r="U9" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="T9" s="5">
-        <v>1</v>
-      </c>
-      <c r="U9" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="V9" s="5"/>
       <c r="W9" s="5"/>
@@ -1587,22 +1584,22 @@
       <c r="AL9" s="5"/>
       <c r="AM9" s="5"/>
     </row>
-    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
       <c r="B10" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -1622,22 +1619,22 @@
       </c>
       <c r="O10" s="5"/>
       <c r="P10" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>1</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="S10" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="Q10" s="5">
-        <v>1</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="S10" s="5" t="s">
+      <c r="T10" s="5">
+        <v>1</v>
+      </c>
+      <c r="U10" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="T10" s="5">
-        <v>1</v>
-      </c>
-      <c r="U10" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="V10" s="5"/>
       <c r="W10" s="5"/>
@@ -1658,26 +1655,26 @@
       <c r="AL10" s="5"/>
       <c r="AM10" s="5"/>
     </row>
-    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5" t="s">
@@ -1686,12 +1683,12 @@
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
       <c r="P11" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q11" s="5">
         <v>1</v>
@@ -1718,13 +1715,13 @@
       <c r="AC11" s="5"/>
       <c r="AD11" s="5"/>
       <c r="AE11" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF11" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="AF11" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="AG11" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AH11" s="5">
         <v>1.1366719999999999</v>
@@ -1743,26 +1740,26 @@
       </c>
       <c r="AM11" s="5"/>
     </row>
-    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5" t="s">
@@ -1771,12 +1768,12 @@
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
       <c r="P12" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q12" s="5">
         <v>30</v>
@@ -1803,13 +1800,13 @@
       <c r="AC12" s="5"/>
       <c r="AD12" s="5"/>
       <c r="AE12" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AF12" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AG12" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AH12" s="5">
         <v>1.101672</v>
@@ -1828,26 +1825,26 @@
       </c>
       <c r="AM12" s="5"/>
     </row>
-    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
       <c r="B13" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>75</v>
+        <v>144</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5" t="s">
@@ -1856,12 +1853,12 @@
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
       <c r="P13" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q13" s="5">
         <v>1</v>
@@ -1888,13 +1885,13 @@
       <c r="AC13" s="5"/>
       <c r="AD13" s="5"/>
       <c r="AE13" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AF13" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AG13" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AH13" s="5"/>
       <c r="AI13" s="5"/>
@@ -1909,26 +1906,26 @@
       </c>
       <c r="AM13" s="5"/>
     </row>
-    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="B14" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>75</v>
+        <v>144</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5" t="s">
@@ -1937,12 +1934,12 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
       <c r="P14" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q14" s="5">
         <v>30</v>
@@ -1969,13 +1966,13 @@
       <c r="AC14" s="5"/>
       <c r="AD14" s="5"/>
       <c r="AE14" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AF14" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AG14" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AH14" s="5"/>
       <c r="AI14" s="5"/>
@@ -1990,26 +1987,26 @@
       </c>
       <c r="AM14" s="5"/>
     </row>
-    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="B15" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5" t="s">
@@ -2018,12 +2015,12 @@
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
       <c r="M15" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
       <c r="P15" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q15" s="5">
         <v>1</v>
@@ -2050,13 +2047,13 @@
       <c r="AC15" s="5"/>
       <c r="AD15" s="5"/>
       <c r="AE15" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AF15" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AG15" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AH15" s="5">
         <v>1.4620299999999999</v>
@@ -2075,26 +2072,26 @@
       </c>
       <c r="AM15" s="5"/>
     </row>
-    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
       <c r="B16" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5" t="s">
@@ -2103,12 +2100,12 @@
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
       <c r="P16" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q16" s="5">
         <v>30</v>
@@ -2135,13 +2132,13 @@
       <c r="AC16" s="5"/>
       <c r="AD16" s="5"/>
       <c r="AE16" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AF16" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AG16" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AH16" s="5">
         <v>1.4620299999999999</v>
@@ -2160,26 +2157,26 @@
       </c>
       <c r="AM16" s="5"/>
     </row>
-    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="B17" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5" t="s">
@@ -2188,12 +2185,12 @@
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
       <c r="M17" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
       <c r="P17" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q17" s="5">
         <v>1</v>
@@ -2220,13 +2217,13 @@
       <c r="AC17" s="5"/>
       <c r="AD17" s="5"/>
       <c r="AE17" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AF17" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AG17" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AH17" s="5"/>
       <c r="AI17" s="5"/>
@@ -2241,26 +2238,26 @@
       </c>
       <c r="AM17" s="5"/>
     </row>
-    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5" t="s">
@@ -2269,12 +2266,12 @@
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q18" s="5">
         <v>30</v>
@@ -2301,13 +2298,13 @@
       <c r="AC18" s="5"/>
       <c r="AD18" s="5"/>
       <c r="AE18" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AF18" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AG18" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AH18" s="5"/>
       <c r="AI18" s="5"/>
@@ -2322,26 +2319,26 @@
       </c>
       <c r="AM18" s="5"/>
     </row>
-    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="5"/>
       <c r="B19" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5" t="s">
@@ -2350,12 +2347,12 @@
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
       <c r="P19" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q19" s="5">
         <v>1</v>
@@ -2382,13 +2379,13 @@
       <c r="AC19" s="5"/>
       <c r="AD19" s="5"/>
       <c r="AE19" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AF19" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AG19" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AH19" s="5"/>
       <c r="AI19" s="5"/>
@@ -2403,26 +2400,26 @@
       </c>
       <c r="AM19" s="5"/>
     </row>
-    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
       <c r="B20" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5" t="s">
@@ -2431,12 +2428,12 @@
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
       <c r="M20" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q20" s="5">
         <v>1</v>
@@ -2463,13 +2460,13 @@
       <c r="AC20" s="5"/>
       <c r="AD20" s="5"/>
       <c r="AE20" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AF20" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AG20" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AH20" s="5"/>
       <c r="AI20" s="5"/>
@@ -2484,26 +2481,26 @@
       </c>
       <c r="AM20" s="5"/>
     </row>
-    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
       <c r="B21" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5" t="s">
@@ -2512,12 +2509,12 @@
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
       <c r="P21" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q21" s="5">
         <v>30</v>
@@ -2544,13 +2541,13 @@
       <c r="AC21" s="5"/>
       <c r="AD21" s="5"/>
       <c r="AE21" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AF21" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AG21" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AH21" s="5"/>
       <c r="AI21" s="5"/>
@@ -2565,24 +2562,24 @@
       </c>
       <c r="AM21" s="5"/>
     </row>
-    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5" t="s">
@@ -2591,12 +2588,12 @@
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q22" s="5">
         <v>1</v>
@@ -2623,13 +2620,13 @@
       <c r="AC22" s="5"/>
       <c r="AD22" s="5"/>
       <c r="AE22" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF22" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AG22" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="AF22" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="AG22" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="AH22" s="5"/>
       <c r="AI22" s="5"/>
@@ -2638,24 +2635,24 @@
       <c r="AL22" s="5"/>
       <c r="AM22" s="5"/>
     </row>
-    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5" t="s">
@@ -2664,12 +2661,12 @@
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
       <c r="P23" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q23" s="5">
         <v>30</v>
@@ -2696,13 +2693,13 @@
       <c r="AC23" s="5"/>
       <c r="AD23" s="5"/>
       <c r="AE23" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AF23" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AG23" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AH23" s="5"/>
       <c r="AI23" s="5"/>
@@ -2711,19 +2708,19 @@
       <c r="AL23" s="5"/>
       <c r="AM23" s="5"/>
     </row>
-    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
       <c r="B24" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -2734,7 +2731,7 @@
       </c>
       <c r="K24" s="5"/>
       <c r="L24" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M24" s="5" t="s">
         <v>49</v>
@@ -2744,7 +2741,7 @@
         <v>1.5</v>
       </c>
       <c r="P24" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q24" s="5">
         <v>30</v>
@@ -2780,19 +2777,19 @@
       <c r="AL24" s="5"/>
       <c r="AM24" s="5"/>
     </row>
-    <row r="25" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -2803,7 +2800,7 @@
       </c>
       <c r="K25" s="5"/>
       <c r="L25" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M25" s="5" t="s">
         <v>49</v>
@@ -2813,7 +2810,7 @@
         <v>3.1</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q25" s="5">
         <v>30</v>
@@ -2849,24 +2846,24 @@
       <c r="AL25" s="5"/>
       <c r="AM25" s="5"/>
     </row>
-    <row r="26" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
       <c r="B26" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5" t="s">
@@ -2882,7 +2879,7 @@
         <v>20000</v>
       </c>
       <c r="P26" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q26" s="5">
         <v>30</v>
@@ -2918,24 +2915,24 @@
       <c r="AL26" s="5"/>
       <c r="AM26" s="5"/>
     </row>
-    <row r="27" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
       <c r="B27" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5" t="s">
@@ -2951,7 +2948,7 @@
         <v>340</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q27" s="5">
         <v>1</v>
@@ -2987,24 +2984,24 @@
       <c r="AL27" s="5"/>
       <c r="AM27" s="5"/>
     </row>
-    <row r="28" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
       <c r="B28" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I28" s="5"/>
       <c r="J28" s="5" t="s">
@@ -3020,7 +3017,7 @@
         <v>150</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q28" s="5">
         <v>30</v>
@@ -3056,24 +3053,24 @@
       <c r="AL28" s="5"/>
       <c r="AM28" s="5"/>
     </row>
-    <row r="29" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5" t="s">
@@ -3089,7 +3086,7 @@
         <v>860000</v>
       </c>
       <c r="P29" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q29" s="5">
         <v>1</v>
@@ -3125,24 +3122,24 @@
       <c r="AL29" s="5"/>
       <c r="AM29" s="5"/>
     </row>
-    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I30" s="5"/>
       <c r="J30" s="5" t="s">
@@ -3158,7 +3155,7 @@
         <v>230000</v>
       </c>
       <c r="P30" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q30" s="5">
         <v>30</v>
@@ -3194,26 +3191,26 @@
       <c r="AL30" s="5"/>
       <c r="AM30" s="5"/>
     </row>
-    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I31" s="5"/>
       <c r="J31" s="5" t="s">
@@ -3229,7 +3226,7 @@
         <v>19</v>
       </c>
       <c r="P31" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q31" s="5">
         <v>1</v>
@@ -3265,26 +3262,26 @@
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
     </row>
-    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I32" s="5"/>
       <c r="J32" s="5" t="s">
@@ -3300,7 +3297,7 @@
         <v>11</v>
       </c>
       <c r="P32" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q32" s="5">
         <v>30</v>
@@ -3336,26 +3333,26 @@
       <c r="AL32" s="5"/>
       <c r="AM32" s="5"/>
     </row>
-    <row r="33" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="5" t="s">
@@ -3371,7 +3368,7 @@
         <v>16</v>
       </c>
       <c r="P33" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q33" s="5">
         <v>1</v>
@@ -3407,26 +3404,26 @@
       <c r="AL33" s="5"/>
       <c r="AM33" s="5"/>
     </row>
-    <row r="34" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
       <c r="B34" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I34" s="5"/>
       <c r="J34" s="5" t="s">
@@ -3442,7 +3439,7 @@
         <v>11</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q34" s="5">
         <v>30</v>
@@ -3478,24 +3475,24 @@
       <c r="AL34" s="5"/>
       <c r="AM34" s="5"/>
     </row>
-    <row r="35" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="5"/>
       <c r="B35" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I35" s="5"/>
       <c r="J35" s="5" t="s">
@@ -3511,7 +3508,7 @@
         <v>22</v>
       </c>
       <c r="P35" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q35" s="5">
         <v>1</v>
@@ -3547,24 +3544,24 @@
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
     </row>
-    <row r="36" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="5"/>
       <c r="B36" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I36" s="5"/>
       <c r="J36" s="5" t="s">
@@ -3580,7 +3577,7 @@
         <v>5.2</v>
       </c>
       <c r="P36" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q36" s="5">
         <v>30</v>
@@ -3616,24 +3613,24 @@
       <c r="AL36" s="5"/>
       <c r="AM36" s="5"/>
     </row>
-    <row r="37" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
       <c r="B37" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5" t="s">
@@ -3649,7 +3646,7 @@
         <v>1000</v>
       </c>
       <c r="P37" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q37" s="5">
         <v>30</v>
@@ -3685,24 +3682,24 @@
       <c r="AL37" s="5"/>
       <c r="AM37" s="5"/>
     </row>
-    <row r="38" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="5"/>
       <c r="B38" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
       <c r="H38" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I38" s="5"/>
       <c r="J38" s="5" t="s">
@@ -3718,7 +3715,7 @@
         <v>1.4</v>
       </c>
       <c r="P38" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q38" s="5">
         <v>1</v>
@@ -3754,24 +3751,24 @@
       <c r="AL38" s="5"/>
       <c r="AM38" s="5"/>
     </row>
-    <row r="39" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="5"/>
       <c r="B39" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I39" s="5"/>
       <c r="J39" s="5" t="s">
@@ -3789,7 +3786,7 @@
         <v>9</v>
       </c>
       <c r="P39" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="Q39" s="5">
         <v>7</v>
@@ -3798,13 +3795,13 @@
         <v>54</v>
       </c>
       <c r="S39" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="T39" s="5">
         <v>1</v>
       </c>
       <c r="U39" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="V39" s="5"/>
       <c r="W39" s="5"/>
@@ -3825,24 +3822,24 @@
       <c r="AL39" s="5"/>
       <c r="AM39" s="5"/>
     </row>
-    <row r="40" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="5"/>
       <c r="B40" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I40" s="5"/>
       <c r="J40" s="5" t="s">
@@ -3858,7 +3855,7 @@
         <v>2</v>
       </c>
       <c r="P40" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q40" s="5">
         <v>30</v>
@@ -3894,19 +3891,19 @@
       <c r="AL40" s="5"/>
       <c r="AM40" s="5"/>
     </row>
-    <row r="41" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="5"/>
       <c r="B41" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -3925,7 +3922,7 @@
         <v>5.6</v>
       </c>
       <c r="P41" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q41" s="5">
         <v>1</v>
@@ -3961,19 +3958,19 @@
       <c r="AL41" s="5"/>
       <c r="AM41" s="5"/>
     </row>
-    <row r="42" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D42" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>131</v>
-      </c>
       <c r="E42" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -3992,7 +3989,7 @@
         <v>640</v>
       </c>
       <c r="P42" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q42" s="5">
         <v>30</v>
@@ -4028,19 +4025,19 @@
       <c r="AL42" s="5"/>
       <c r="AM42" s="5"/>
     </row>
-    <row r="43" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -4059,7 +4056,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="P43" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q43" s="5">
         <v>1</v>
@@ -4095,19 +4092,19 @@
       <c r="AL43" s="5"/>
       <c r="AM43" s="5"/>
     </row>
-    <row r="44" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -4126,7 +4123,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P44" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q44" s="5">
         <v>30</v>
@@ -4162,19 +4159,19 @@
       <c r="AL44" s="5"/>
       <c r="AM44" s="5"/>
     </row>
-    <row r="45" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -4193,7 +4190,7 @@
         <v>7000000</v>
       </c>
       <c r="P45" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="Q45" s="5">
         <v>1</v>
@@ -4229,19 +4226,19 @@
       <c r="AL45" s="5"/>
       <c r="AM45" s="5"/>
     </row>
-    <row r="46" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -4260,7 +4257,7 @@
         <v>1000</v>
       </c>
       <c r="P46" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q46" s="5">
         <v>1</v>
@@ -4296,19 +4293,19 @@
       <c r="AL46" s="5"/>
       <c r="AM46" s="5"/>
     </row>
-    <row r="47" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -4327,7 +4324,7 @@
         <v>1300</v>
       </c>
       <c r="P47" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q47" s="5">
         <v>1</v>
@@ -4363,19 +4360,19 @@
       <c r="AL47" s="5"/>
       <c r="AM47" s="5"/>
     </row>
-    <row r="48" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -4394,7 +4391,7 @@
         <v>4</v>
       </c>
       <c r="P48" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q48" s="5">
         <v>1</v>
@@ -4430,19 +4427,19 @@
       <c r="AL48" s="5"/>
       <c r="AM48" s="5"/>
     </row>
-    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -4461,7 +4458,7 @@
         <v>400</v>
       </c>
       <c r="P49" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q49" s="5">
         <v>30</v>
@@ -4497,19 +4494,19 @@
       <c r="AL49" s="5"/>
       <c r="AM49" s="5"/>
     </row>
-    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -4528,7 +4525,7 @@
         <v>50</v>
       </c>
       <c r="P50" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q50" s="5">
         <v>1</v>
@@ -4564,19 +4561,19 @@
       <c r="AL50" s="5"/>
       <c r="AM50" s="5"/>
     </row>
-    <row r="51" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -4595,7 +4592,7 @@
         <v>100</v>
       </c>
       <c r="P51" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q51" s="5">
         <v>30</v>
@@ -4631,19 +4628,19 @@
       <c r="AL51" s="5"/>
       <c r="AM51" s="5"/>
     </row>
-    <row r="52" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="5"/>
       <c r="B52" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -4662,7 +4659,7 @@
         <v>0.3</v>
       </c>
       <c r="P52" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="Q52" s="5">
         <v>30</v>
@@ -4698,19 +4695,19 @@
       <c r="AL52" s="5"/>
       <c r="AM52" s="5"/>
     </row>
-    <row r="53" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="5"/>
       <c r="B53" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -4729,7 +4726,7 @@
         <v>0.3</v>
       </c>
       <c r="P53" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="Q53" s="5">
         <v>30</v>
@@ -4765,19 +4762,19 @@
       <c r="AL53" s="5"/>
       <c r="AM53" s="5"/>
     </row>
-    <row r="54" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="5"/>
       <c r="B54" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -4796,7 +4793,7 @@
         <v>610</v>
       </c>
       <c r="P54" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q54" s="5">
         <v>1</v>
@@ -4832,19 +4829,19 @@
       <c r="AL54" s="5"/>
       <c r="AM54" s="5"/>
     </row>
-    <row r="55" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -4863,7 +4860,7 @@
         <v>4600</v>
       </c>
       <c r="P55" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q55" s="5">
         <v>30</v>
@@ -4899,19 +4896,19 @@
       <c r="AL55" s="5"/>
       <c r="AM55" s="5"/>
     </row>
-    <row r="56" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -4930,7 +4927,7 @@
         <v>10000</v>
       </c>
       <c r="P56" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q56" s="5">
         <v>1</v>
@@ -4966,19 +4963,19 @@
       <c r="AL56" s="5"/>
       <c r="AM56" s="5"/>
     </row>
-    <row r="57" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -4999,7 +4996,7 @@
         <v>9</v>
       </c>
       <c r="P57" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="Q57" s="5">
         <v>1</v>
@@ -5008,13 +5005,13 @@
         <v>54</v>
       </c>
       <c r="S57" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="T57" s="5">
         <v>1</v>
       </c>
       <c r="U57" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="V57" s="5"/>
       <c r="W57" s="5"/>
@@ -5035,19 +5032,19 @@
       <c r="AL57" s="5"/>
       <c r="AM57" s="5"/>
     </row>
-    <row r="58" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="5"/>
       <c r="B58" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -5066,7 +5063,7 @@
         <v>170</v>
       </c>
       <c r="P58" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q58" s="5">
         <v>1</v>
@@ -5102,19 +5099,19 @@
       <c r="AL58" s="5"/>
       <c r="AM58" s="5"/>
     </row>
-    <row r="59" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
@@ -5133,7 +5130,7 @@
         <v>4200</v>
       </c>
       <c r="P59" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q59" s="5">
         <v>30</v>
@@ -5169,7 +5166,7 @@
       <c r="AL59" s="5"/>
       <c r="AM59" s="5"/>
     </row>
-    <row r="60" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5" t="s">
         <v>43</v>
@@ -5178,13 +5175,13 @@
         <v>147</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -5202,7 +5199,7 @@
         <v>250000</v>
       </c>
       <c r="P60" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q60" s="5">
         <v>1</v>
@@ -5238,19 +5235,19 @@
       <c r="AL60" s="5"/>
       <c r="AM60" s="5"/>
     </row>
-    <row r="61" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
@@ -5269,7 +5266,7 @@
         <v>7400</v>
       </c>
       <c r="P61" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q61" s="5">
         <v>1</v>
@@ -5305,19 +5302,19 @@
       <c r="AL61" s="5"/>
       <c r="AM61" s="5"/>
     </row>
-    <row r="62" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
@@ -5336,7 +5333,7 @@
         <v>26000</v>
       </c>
       <c r="P62" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q62" s="5">
         <v>30</v>

--- a/inst/extdata/southern_ute_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/southern_ute_tribe_criteria_crosswalk.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D29BD9-C78F-4910-81E6-3B904012C5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEF3528-792A-48B6-812F-47589C426B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8519E9F5-E322-41EB-A2D9-94E5D3901206}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="20710" windowHeight="11020" xr2:uid="{8519E9F5-E322-41EB-A2D9-94E5D3901206}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="147">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -416,15 +416,9 @@
     <t>Antimony</t>
   </si>
   <si>
-    <t>Human Health - Water + organism</t>
-  </si>
-  <si>
     <t>ANTIMONY</t>
   </si>
   <si>
-    <t>Human Health - Organism</t>
-  </si>
-  <si>
     <t>Asbestos</t>
   </si>
   <si>
@@ -480,6 +474,9 @@
   </si>
   <si>
     <t>TOTAL DISSOLVED SOLIDS (TDS)</t>
+  </si>
+  <si>
+    <t>Drinking Water</t>
   </si>
 </sst>
 </file>
@@ -890,6 +887,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C89350-85A2-44F8-BF86-837CAD77A8FE}">
   <dimension ref="A1:AQ62"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="31.6328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:43" s="4" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -1448,7 +1448,7 @@
         <v>43</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>45</v>
@@ -1519,7 +1519,7 @@
         <v>43</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>45</v>
@@ -1590,7 +1590,7 @@
         <v>43</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>45</v>
@@ -1831,7 +1831,7 @@
         <v>43</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>45</v>
@@ -1912,7 +1912,7 @@
         <v>43</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>45</v>
@@ -3339,7 +3339,7 @@
         <v>43</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>45</v>
@@ -3410,7 +3410,7 @@
         <v>43</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>45</v>
@@ -3900,10 +3900,10 @@
         <v>125</v>
       </c>
       <c r="D41" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>127</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -3967,10 +3967,10 @@
         <v>125</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -4034,7 +4034,7 @@
         <v>105</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>106</v>
@@ -4101,7 +4101,7 @@
         <v>105</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>106</v>
@@ -4165,13 +4165,13 @@
         <v>43</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -4190,7 +4190,7 @@
         <v>7000000</v>
       </c>
       <c r="P45" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="Q45" s="5">
         <v>1</v>
@@ -4232,13 +4232,13 @@
         <v>43</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -4299,13 +4299,13 @@
         <v>43</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -4369,7 +4369,7 @@
         <v>113</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>114</v>
@@ -4436,7 +4436,7 @@
         <v>113</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>114</v>
@@ -4500,13 +4500,13 @@
         <v>43</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -4567,13 +4567,13 @@
         <v>43</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -4634,13 +4634,13 @@
         <v>43</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -4659,7 +4659,7 @@
         <v>0.3</v>
       </c>
       <c r="P52" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="Q52" s="5">
         <v>30</v>
@@ -4701,13 +4701,13 @@
         <v>43</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -4726,7 +4726,7 @@
         <v>0.3</v>
       </c>
       <c r="P53" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="Q53" s="5">
         <v>30</v>
@@ -4771,7 +4771,7 @@
         <v>81</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>82</v>
@@ -4838,7 +4838,7 @@
         <v>81</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>82</v>
@@ -4902,13 +4902,13 @@
         <v>43</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -4972,7 +4972,7 @@
         <v>119</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>120</v>
@@ -5041,7 +5041,7 @@
         <v>99</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>100</v>
@@ -5108,7 +5108,7 @@
         <v>99</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>100</v>
@@ -5172,13 +5172,13 @@
         <v>43</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>111</v>
@@ -5244,7 +5244,7 @@
         <v>88</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>89</v>
@@ -5311,7 +5311,7 @@
         <v>88</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="E62" s="5" t="s">
         <v>89</v>

--- a/inst/extdata/southern_ute_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/southern_ute_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/sheila_saia_tetratech_com/Documents/Documents/github/TADACommunityHub/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{4EEF3528-792A-48B6-812F-47589C426B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{289E164F-B0A4-4CEF-9670-CD6E47C5F039}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4902D57-D970-4C90-A4A9-B70A87CC04B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8519E9F5-E322-41EB-A2D9-94E5D3901206}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8519E9F5-E322-41EB-A2D9-94E5D3901206}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -871,14 +871,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C89350-85A2-44F8-BF86-837CAD77A8FE}">
   <dimension ref="A1:AP62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="9.140625" style="5"/>
-    <col min="4" max="4" width="31.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="3" width="9.1796875" style="5"/>
+    <col min="4" max="4" width="31.54296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.1796875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>42</v>
@@ -1074,7 +1074,7 @@
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
     </row>
-    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>42</v>
@@ -1142,7 +1142,7 @@
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
     </row>
-    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>42</v>
@@ -1210,7 +1210,7 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
     </row>
-    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>42</v>
@@ -1278,7 +1278,7 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
     </row>
-    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>42</v>
@@ -1346,7 +1346,7 @@
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
     </row>
-    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>42</v>
@@ -1414,7 +1414,7 @@
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
     </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>42</v>
@@ -1484,7 +1484,7 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
     </row>
-    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>42</v>
@@ -1554,7 +1554,7 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
     </row>
-    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>42</v>
@@ -1624,7 +1624,7 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
     </row>
-    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>42</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>42</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AL12" s="3"/>
     </row>
-    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>42</v>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="AL13" s="3"/>
     </row>
-    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>42</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AL14" s="3"/>
     </row>
-    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>42</v>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="AL15" s="3"/>
     </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>42</v>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>42</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="AL17" s="3"/>
     </row>
-    <row r="18" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>42</v>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="AL18" s="3"/>
     </row>
-    <row r="19" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>42</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>42</v>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="AL20" s="3"/>
     </row>
-    <row r="21" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>42</v>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AL21" s="3"/>
     </row>
-    <row r="22" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>42</v>
@@ -2568,7 +2568,7 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
     </row>
-    <row r="23" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>42</v>
@@ -2638,7 +2638,7 @@
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
     </row>
-    <row r="24" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>42</v>
@@ -2706,7 +2706,7 @@
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
     </row>
-    <row r="25" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>42</v>
@@ -2774,7 +2774,7 @@
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
     </row>
-    <row r="26" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>42</v>
@@ -2842,7 +2842,7 @@
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
     </row>
-    <row r="27" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>42</v>
@@ -2910,7 +2910,7 @@
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
     </row>
-    <row r="28" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>42</v>
@@ -2978,7 +2978,7 @@
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
     </row>
-    <row r="29" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>42</v>
@@ -3046,7 +3046,7 @@
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
-    <row r="30" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>42</v>
@@ -3114,7 +3114,7 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
     </row>
-    <row r="31" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>42</v>
@@ -3184,7 +3184,7 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
     </row>
-    <row r="32" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>42</v>
@@ -3254,7 +3254,7 @@
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
     </row>
-    <row r="33" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>42</v>
@@ -3324,7 +3324,7 @@
       <c r="AK33" s="3"/>
       <c r="AL33" s="3"/>
     </row>
-    <row r="34" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>42</v>
@@ -3394,7 +3394,7 @@
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
     </row>
-    <row r="35" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>42</v>
@@ -3462,7 +3462,7 @@
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
     </row>
-    <row r="36" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>42</v>
@@ -3530,7 +3530,7 @@
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
     </row>
-    <row r="37" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>42</v>
@@ -3598,7 +3598,7 @@
       <c r="AK37" s="3"/>
       <c r="AL37" s="3"/>
     </row>
-    <row r="38" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
         <v>42</v>
@@ -3666,7 +3666,7 @@
       <c r="AK38" s="3"/>
       <c r="AL38" s="3"/>
     </row>
-    <row r="39" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>42</v>
@@ -3736,7 +3736,7 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
         <v>42</v>
@@ -3804,7 +3804,7 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>42</v>
@@ -3870,7 +3870,7 @@
       <c r="AK41" s="3"/>
       <c r="AL41" s="3"/>
     </row>
-    <row r="42" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>42</v>
@@ -3936,7 +3936,7 @@
       <c r="AK42" s="3"/>
       <c r="AL42" s="3"/>
     </row>
-    <row r="43" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>42</v>
@@ -4002,7 +4002,7 @@
       <c r="AK43" s="3"/>
       <c r="AL43" s="3"/>
     </row>
-    <row r="44" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
         <v>42</v>
@@ -4068,7 +4068,7 @@
       <c r="AK44" s="3"/>
       <c r="AL44" s="3"/>
     </row>
-    <row r="45" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>42</v>
@@ -4134,7 +4134,7 @@
       <c r="AK45" s="3"/>
       <c r="AL45" s="3"/>
     </row>
-    <row r="46" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
         <v>42</v>
@@ -4200,7 +4200,7 @@
       <c r="AK46" s="3"/>
       <c r="AL46" s="3"/>
     </row>
-    <row r="47" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>42</v>
@@ -4266,7 +4266,7 @@
       <c r="AK47" s="3"/>
       <c r="AL47" s="3"/>
     </row>
-    <row r="48" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
         <v>42</v>
@@ -4332,7 +4332,7 @@
       <c r="AK48" s="3"/>
       <c r="AL48" s="3"/>
     </row>
-    <row r="49" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
         <v>42</v>
@@ -4398,7 +4398,7 @@
       <c r="AK49" s="3"/>
       <c r="AL49" s="3"/>
     </row>
-    <row r="50" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
         <v>42</v>
@@ -4464,7 +4464,7 @@
       <c r="AK50" s="3"/>
       <c r="AL50" s="3"/>
     </row>
-    <row r="51" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
         <v>42</v>
@@ -4530,7 +4530,7 @@
       <c r="AK51" s="3"/>
       <c r="AL51" s="3"/>
     </row>
-    <row r="52" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
         <v>42</v>
@@ -4596,7 +4596,7 @@
       <c r="AK52" s="3"/>
       <c r="AL52" s="3"/>
     </row>
-    <row r="53" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
         <v>42</v>
@@ -4662,7 +4662,7 @@
       <c r="AK53" s="3"/>
       <c r="AL53" s="3"/>
     </row>
-    <row r="54" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
         <v>42</v>
@@ -4728,7 +4728,7 @@
       <c r="AK54" s="3"/>
       <c r="AL54" s="3"/>
     </row>
-    <row r="55" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
         <v>42</v>
@@ -4794,7 +4794,7 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
         <v>42</v>
@@ -4860,7 +4860,7 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
         <v>42</v>
@@ -4928,7 +4928,7 @@
       <c r="AK57" s="3"/>
       <c r="AL57" s="3"/>
     </row>
-    <row r="58" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
         <v>42</v>
@@ -4994,7 +4994,7 @@
       <c r="AK58" s="3"/>
       <c r="AL58" s="3"/>
     </row>
-    <row r="59" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
         <v>42</v>
@@ -5060,7 +5060,7 @@
       <c r="AK59" s="3"/>
       <c r="AL59" s="3"/>
     </row>
-    <row r="60" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
         <v>42</v>
@@ -5128,7 +5128,7 @@
       <c r="AK60" s="3"/>
       <c r="AL60" s="3"/>
     </row>
-    <row r="61" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
         <v>42</v>
@@ -5194,7 +5194,7 @@
       <c r="AK61" s="3"/>
       <c r="AL61" s="3"/>
     </row>
-    <row r="62" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
         <v>42</v>

--- a/inst/extdata/southern_ute_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/southern_ute_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4902D57-D970-4C90-A4A9-B70A87CC04B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D8CFAA-70F5-488B-AAC3-231A0186786E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8519E9F5-E322-41EB-A2D9-94E5D3901206}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{8519E9F5-E322-41EB-A2D9-94E5D3901206}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,9 +131,6 @@
     <t>EquationType</t>
   </si>
   <si>
-    <t>Equation</t>
-  </si>
-  <si>
     <t>hardness_param_1</t>
   </si>
   <si>
@@ -465,6 +462,9 @@
   </si>
   <si>
     <t>0.986*(e^(0.8473*(ln(hardness))+0.884))</t>
+  </si>
+  <si>
+    <t>EquationFormula</t>
   </si>
 </sst>
 </file>
@@ -871,14 +871,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C89350-85A2-44F8-BF86-837CAD77A8FE}">
   <dimension ref="A1:AP62"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="9.1796875" style="5"/>
-    <col min="4" max="4" width="31.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.1796875" style="5"/>
+    <col min="1" max="3" width="9.140625" style="5"/>
+    <col min="4" max="4" width="31.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -973,88 +973,88 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="N2" s="3">
         <v>20</v>
       </c>
       <c r="O2" s="3"/>
       <c r="P2" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q2" s="3">
         <v>2</v>
       </c>
       <c r="R2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="S2" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="T2" s="3">
         <v>1</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -1074,55 +1074,55 @@
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
     </row>
-    <row r="3" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="N3" s="3">
         <v>17</v>
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q3" s="3">
         <v>7</v>
       </c>
       <c r="R3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S3" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T3" s="3">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -1142,55 +1142,55 @@
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
     </row>
-    <row r="4" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N4" s="3">
         <v>24</v>
       </c>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q4" s="3">
         <v>2</v>
       </c>
       <c r="R4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="S4" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="T4" s="3">
         <v>1</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -1210,55 +1210,55 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
     </row>
-    <row r="5" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N5" s="3">
         <v>21</v>
       </c>
       <c r="O5" s="3"/>
       <c r="P5" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q5" s="3">
         <v>7</v>
       </c>
       <c r="R5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S5" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S5" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T5" s="3">
         <v>1</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -1278,55 +1278,55 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
     </row>
-    <row r="6" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N6" s="3">
         <v>30</v>
       </c>
       <c r="O6" s="3"/>
       <c r="P6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="3">
         <v>2</v>
       </c>
       <c r="R6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="S6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="S6" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="T6" s="3">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -1346,55 +1346,55 @@
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
     </row>
-    <row r="7" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N7" s="3">
         <v>27</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q7" s="3">
         <v>7</v>
       </c>
       <c r="R7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S7" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S7" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T7" s="3">
         <v>1</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
@@ -1414,57 +1414,57 @@
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
     </row>
-    <row r="8" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="N8" s="3">
         <v>6</v>
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>1</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="Q8" s="3">
-        <v>1</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="S8" s="3" t="s">
+      <c r="T8" s="3">
+        <v>1</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="T8" s="3">
-        <v>1</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
@@ -1484,57 +1484,57 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
     </row>
-    <row r="9" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N9" s="3">
         <v>6</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>1</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="Q9" s="3">
-        <v>1</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="S9" s="3" t="s">
+      <c r="T9" s="3">
+        <v>1</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="T9" s="3">
-        <v>1</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
@@ -1554,57 +1554,57 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
     </row>
-    <row r="10" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N10" s="3">
         <v>5</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="Q10" s="3">
-        <v>1</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="S10" s="3" t="s">
+      <c r="T10" s="3">
+        <v>1</v>
+      </c>
+      <c r="U10" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
@@ -1624,55 +1624,55 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
     </row>
-    <row r="11" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q11" s="3">
         <v>1</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T11" s="3">
         <v>1</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
@@ -1684,10 +1684,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AF11" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG11" s="3">
         <v>1.1366719999999999</v>
@@ -1706,55 +1706,55 @@
       </c>
       <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q12" s="3">
         <v>30</v>
       </c>
       <c r="R12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T12" s="3">
         <v>1</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
@@ -1766,10 +1766,10 @@
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AF12" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AG12" s="3">
         <v>1.101672</v>
@@ -1788,55 +1788,55 @@
       </c>
       <c r="AL12" s="3"/>
     </row>
-    <row r="13" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q13" s="3">
         <v>1</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T13" s="3">
         <v>1</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
@@ -1848,10 +1848,10 @@
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AF13" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AG13" s="3"/>
       <c r="AH13" s="3"/>
@@ -1866,55 +1866,55 @@
       </c>
       <c r="AL13" s="3"/>
     </row>
-    <row r="14" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q14" s="3">
         <v>30</v>
       </c>
       <c r="R14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T14" s="3">
         <v>1</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
@@ -1926,10 +1926,10 @@
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AF14" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AG14" s="3"/>
       <c r="AH14" s="3"/>
@@ -1944,55 +1944,55 @@
       </c>
       <c r="AL14" s="3"/>
     </row>
-    <row r="15" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q15" s="3">
         <v>1</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T15" s="3">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
@@ -2004,10 +2004,10 @@
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AG15" s="3">
         <v>1.4620299999999999</v>
@@ -2026,55 +2026,55 @@
       </c>
       <c r="AL15" s="3"/>
     </row>
-    <row r="16" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q16" s="3">
         <v>30</v>
       </c>
       <c r="R16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S16" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T16" s="3">
         <v>1</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -2086,10 +2086,10 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AF16" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG16" s="3">
         <v>1.4620299999999999</v>
@@ -2108,55 +2108,55 @@
       </c>
       <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="F17" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q17" s="3">
         <v>1</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T17" s="3">
         <v>1</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -2168,10 +2168,10 @@
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AF17" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG17" s="3"/>
       <c r="AH17" s="3"/>
@@ -2186,55 +2186,55 @@
       </c>
       <c r="AL17" s="3"/>
     </row>
-    <row r="18" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q18" s="3">
         <v>30</v>
       </c>
       <c r="R18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S18" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T18" s="3">
         <v>1</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -2246,10 +2246,10 @@
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AF18" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG18" s="3"/>
       <c r="AH18" s="3"/>
@@ -2264,55 +2264,55 @@
       </c>
       <c r="AL18" s="3"/>
     </row>
-    <row r="19" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="F19" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q19" s="3">
         <v>1</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T19" s="3">
         <v>1</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -2324,10 +2324,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AF19" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
@@ -2342,55 +2342,55 @@
       </c>
       <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="F20" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q20" s="3">
         <v>1</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T20" s="3">
         <v>1</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -2402,10 +2402,10 @@
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AF20" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG20" s="3"/>
       <c r="AH20" s="3"/>
@@ -2420,55 +2420,55 @@
       </c>
       <c r="AL20" s="3"/>
     </row>
-    <row r="21" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="F21" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q21" s="3">
         <v>30</v>
       </c>
       <c r="R21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S21" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T21" s="3">
         <v>1</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -2480,10 +2480,10 @@
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AF21" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG21" s="3"/>
       <c r="AH21" s="3"/>
@@ -2498,53 +2498,53 @@
       </c>
       <c r="AL21" s="3"/>
     </row>
-    <row r="22" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q22" s="3">
         <v>1</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T22" s="3">
         <v>1</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -2556,10 +2556,10 @@
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF22" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="AF22" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="AG22" s="3"/>
       <c r="AH22" s="3"/>
@@ -2568,53 +2568,53 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
     </row>
-    <row r="23" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q23" s="3">
         <v>30</v>
       </c>
       <c r="R23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S23" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T23" s="3">
         <v>1</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -2626,10 +2626,10 @@
       <c r="AC23" s="3"/>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AF23" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AG23" s="3"/>
       <c r="AH23" s="3"/>
@@ -2638,55 +2638,55 @@
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
     </row>
-    <row r="24" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3">
         <v>1.5</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q24" s="3">
         <v>30</v>
       </c>
       <c r="R24" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S24" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T24" s="3">
         <v>1</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -2706,55 +2706,55 @@
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
     </row>
-    <row r="25" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3">
         <v>3.1</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q25" s="3">
         <v>30</v>
       </c>
       <c r="R25" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S25" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S25" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T25" s="3">
         <v>1</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -2774,55 +2774,55 @@
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
     </row>
-    <row r="26" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3">
         <v>20000</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q26" s="3">
         <v>30</v>
       </c>
       <c r="R26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S26" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T26" s="3">
         <v>1</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -2842,55 +2842,55 @@
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
     </row>
-    <row r="27" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3">
         <v>340</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q27" s="3">
         <v>1</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T27" s="3">
         <v>1</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -2910,55 +2910,55 @@
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
     </row>
-    <row r="28" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3">
         <v>150</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q28" s="3">
         <v>30</v>
       </c>
       <c r="R28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S28" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S28" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T28" s="3">
         <v>1</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -2978,55 +2978,55 @@
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
     </row>
-    <row r="29" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3">
         <v>860000</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q29" s="3">
         <v>1</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T29" s="3">
         <v>1</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -3046,55 +3046,55 @@
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
-    <row r="30" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3">
         <v>230000</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q30" s="3">
         <v>30</v>
       </c>
       <c r="R30" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S30" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S30" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T30" s="3">
         <v>1</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -3114,57 +3114,57 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
     </row>
-    <row r="31" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3">
         <v>19</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q31" s="3">
         <v>1</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T31" s="3">
         <v>1</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -3184,57 +3184,57 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
     </row>
-    <row r="32" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="3" t="s">
+      <c r="F32" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3">
         <v>11</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q32" s="3">
         <v>30</v>
       </c>
       <c r="R32" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S32" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T32" s="3">
         <v>1</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
@@ -3254,57 +3254,57 @@
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
     </row>
-    <row r="33" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3">
         <v>16</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q33" s="3">
         <v>1</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T33" s="3">
         <v>1</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3324,57 +3324,57 @@
       <c r="AK33" s="3"/>
       <c r="AL33" s="3"/>
     </row>
-    <row r="34" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3">
         <v>11</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q34" s="3">
         <v>30</v>
       </c>
       <c r="R34" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S34" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S34" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T34" s="3">
         <v>1</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
@@ -3394,55 +3394,55 @@
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
     </row>
-    <row r="35" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3">
         <v>22</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q35" s="3">
         <v>1</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T35" s="3">
         <v>1</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -3462,55 +3462,55 @@
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
     </row>
-    <row r="36" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3">
         <v>5.2</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q36" s="3">
         <v>30</v>
       </c>
       <c r="R36" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S36" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S36" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T36" s="3">
         <v>1</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -3530,55 +3530,55 @@
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
     </row>
-    <row r="37" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3">
         <v>1000</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q37" s="3">
         <v>30</v>
       </c>
       <c r="R37" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S37" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S37" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T37" s="3">
         <v>1</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
@@ -3598,55 +3598,55 @@
       <c r="AK37" s="3"/>
       <c r="AL37" s="3"/>
     </row>
-    <row r="38" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3">
         <v>1.4</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q38" s="3">
         <v>1</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T38" s="3">
         <v>1</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
@@ -3666,33 +3666,33 @@
       <c r="AK38" s="3"/>
       <c r="AL38" s="3"/>
     </row>
-    <row r="39" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N39" s="3">
         <v>6.5</v>
@@ -3701,22 +3701,22 @@
         <v>9</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q39" s="3">
         <v>7</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T39" s="3">
         <v>1</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
@@ -3736,55 +3736,55 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3">
         <v>2</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q40" s="3">
         <v>30</v>
       </c>
       <c r="R40" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S40" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S40" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T40" s="3">
         <v>1</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -3804,53 +3804,53 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3">
         <v>5.6</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q41" s="3">
         <v>1</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T41" s="3">
         <v>1</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -3870,53 +3870,53 @@
       <c r="AK41" s="3"/>
       <c r="AL41" s="3"/>
     </row>
-    <row r="42" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3">
         <v>640</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q42" s="3">
         <v>30</v>
       </c>
       <c r="R42" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S42" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T42" s="3">
         <v>1</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
@@ -3936,53 +3936,53 @@
       <c r="AK42" s="3"/>
       <c r="AL42" s="3"/>
     </row>
-    <row r="43" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q43" s="3">
         <v>1</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T43" s="3">
         <v>1</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
@@ -4002,53 +4002,53 @@
       <c r="AK43" s="3"/>
       <c r="AL43" s="3"/>
     </row>
-    <row r="44" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3">
         <v>0.14000000000000001</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q44" s="3">
         <v>30</v>
       </c>
       <c r="R44" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S44" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T44" s="3">
         <v>1</v>
       </c>
       <c r="U44" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
@@ -4068,53 +4068,53 @@
       <c r="AK44" s="3"/>
       <c r="AL44" s="3"/>
     </row>
-    <row r="45" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3">
         <v>7000000</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q45" s="3">
         <v>1</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T45" s="3">
         <v>1</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
@@ -4134,53 +4134,53 @@
       <c r="AK45" s="3"/>
       <c r="AL45" s="3"/>
     </row>
-    <row r="46" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C46" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3">
         <v>1000</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q46" s="3">
         <v>1</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T46" s="3">
         <v>1</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -4200,53 +4200,53 @@
       <c r="AK46" s="3"/>
       <c r="AL46" s="3"/>
     </row>
-    <row r="47" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3">
         <v>1300</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q47" s="3">
         <v>1</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T47" s="3">
         <v>1</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
@@ -4266,53 +4266,53 @@
       <c r="AK47" s="3"/>
       <c r="AL47" s="3"/>
     </row>
-    <row r="48" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C48" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3">
         <v>4</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q48" s="3">
         <v>1</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T48" s="3">
         <v>1</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
@@ -4332,53 +4332,53 @@
       <c r="AK48" s="3"/>
       <c r="AL48" s="3"/>
     </row>
-    <row r="49" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C49" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3">
         <v>400</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q49" s="3">
         <v>30</v>
       </c>
       <c r="R49" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S49" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T49" s="3">
         <v>1</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
@@ -4398,53 +4398,53 @@
       <c r="AK49" s="3"/>
       <c r="AL49" s="3"/>
     </row>
-    <row r="50" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3">
         <v>50</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q50" s="3">
         <v>1</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T50" s="3">
         <v>1</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
@@ -4464,53 +4464,53 @@
       <c r="AK50" s="3"/>
       <c r="AL50" s="3"/>
     </row>
-    <row r="51" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3">
         <v>100</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q51" s="3">
         <v>30</v>
       </c>
       <c r="R51" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S51" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S51" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T51" s="3">
         <v>1</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
@@ -4530,53 +4530,53 @@
       <c r="AK51" s="3"/>
       <c r="AL51" s="3"/>
     </row>
-    <row r="52" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3">
         <v>0.3</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q52" s="3">
         <v>30</v>
       </c>
       <c r="R52" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S52" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T52" s="3">
         <v>1</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
@@ -4596,53 +4596,53 @@
       <c r="AK52" s="3"/>
       <c r="AL52" s="3"/>
     </row>
-    <row r="53" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="3">
         <v>0.3</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q53" s="3">
         <v>30</v>
       </c>
       <c r="R53" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S53" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S53" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T53" s="3">
         <v>1</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
@@ -4662,53 +4662,53 @@
       <c r="AK53" s="3"/>
       <c r="AL53" s="3"/>
     </row>
-    <row r="54" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C54" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3">
         <v>610</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q54" s="3">
         <v>1</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T54" s="3">
         <v>1</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
@@ -4728,53 +4728,53 @@
       <c r="AK54" s="3"/>
       <c r="AL54" s="3"/>
     </row>
-    <row r="55" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3">
         <v>4600</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q55" s="3">
         <v>30</v>
       </c>
       <c r="R55" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S55" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S55" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T55" s="3">
         <v>1</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
@@ -4794,53 +4794,53 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="3">
         <v>10000</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q56" s="3">
         <v>1</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T56" s="3">
         <v>1</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
@@ -4860,31 +4860,31 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C57" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N57" s="3">
         <v>5</v>
@@ -4893,22 +4893,22 @@
         <v>9</v>
       </c>
       <c r="P57" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>1</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S57" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="Q57" s="3">
-        <v>1</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="T57" s="3">
         <v>1</v>
       </c>
       <c r="U57" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
@@ -4928,53 +4928,53 @@
       <c r="AK57" s="3"/>
       <c r="AL57" s="3"/>
     </row>
-    <row r="58" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C58" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
       <c r="M58" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N58" s="3"/>
       <c r="O58" s="3">
         <v>170</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q58" s="3">
         <v>1</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T58" s="3">
         <v>1</v>
       </c>
       <c r="U58" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
@@ -4994,53 +4994,53 @@
       <c r="AK58" s="3"/>
       <c r="AL58" s="3"/>
     </row>
-    <row r="59" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C59" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
       <c r="M59" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N59" s="3"/>
       <c r="O59" s="3">
         <v>4200</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q59" s="3">
         <v>30</v>
       </c>
       <c r="R59" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S59" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T59" s="3">
         <v>1</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
@@ -5060,55 +5060,55 @@
       <c r="AK59" s="3"/>
       <c r="AL59" s="3"/>
     </row>
-    <row r="60" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C60" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="E60" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="3"/>
       <c r="M60" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N60" s="3"/>
       <c r="O60" s="3">
         <v>250000</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q60" s="3">
         <v>1</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T60" s="3">
         <v>1</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V60" s="3"/>
       <c r="W60" s="3"/>
@@ -5128,53 +5128,53 @@
       <c r="AK60" s="3"/>
       <c r="AL60" s="3"/>
     </row>
-    <row r="61" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C61" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E61" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
       <c r="M61" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N61" s="3"/>
       <c r="O61" s="3">
         <v>7400</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q61" s="3">
         <v>1</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T61" s="3">
         <v>1</v>
       </c>
       <c r="U61" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3"/>
@@ -5194,53 +5194,53 @@
       <c r="AK61" s="3"/>
       <c r="AL61" s="3"/>
     </row>
-    <row r="62" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C62" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
       <c r="M62" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N62" s="3"/>
       <c r="O62" s="3">
         <v>26000</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q62" s="3">
         <v>30</v>
       </c>
       <c r="R62" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S62" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="T62" s="3">
         <v>1</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3"/>

--- a/inst/extdata/southern_ute_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/southern_ute_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D8CFAA-70F5-488B-AAC3-231A0186786E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{74D8CFAA-70F5-488B-AAC3-231A0186786E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEEF6E05-65B8-42B6-9CF6-C7B2E0D50C6B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{8519E9F5-E322-41EB-A2D9-94E5D3901206}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8519E9F5-E322-41EB-A2D9-94E5D3901206}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="152">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -143,12 +143,6 @@
     <t>hardness_param_4</t>
   </si>
   <si>
-    <t>hardness_param_5</t>
-  </si>
-  <si>
-    <t>hardness_param_6</t>
-  </si>
-  <si>
     <t>pH_param_1</t>
   </si>
   <si>
@@ -464,7 +458,40 @@
     <t>0.986*(e^(0.8473*(ln(hardness))+0.884))</t>
   </si>
   <si>
-    <t>EquationFormula</t>
+    <t>Equation</t>
+  </si>
+  <si>
+    <t>pHThreshold</t>
+  </si>
+  <si>
+    <t>pHDirection</t>
+  </si>
+  <si>
+    <t>TemperatureExtreme</t>
+  </si>
+  <si>
+    <t>pH_param_9</t>
+  </si>
+  <si>
+    <t>pH_param_8</t>
+  </si>
+  <si>
+    <t>pH_param_7</t>
+  </si>
+  <si>
+    <t>pH_param_6</t>
+  </si>
+  <si>
+    <t>pH_param_5</t>
+  </si>
+  <si>
+    <t>MinEqMagnitude</t>
+  </si>
+  <si>
+    <t>MaxEqMagnitude</t>
+  </si>
+  <si>
+    <t>Max</t>
   </si>
 </sst>
 </file>
@@ -870,15 +897,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C89350-85A2-44F8-BF86-837CAD77A8FE}">
-  <dimension ref="A1:AP62"/>
+  <dimension ref="A1:AX62"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="5"/>
     <col min="4" max="4" width="31.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="5"/>
+    <col min="5" max="30" width="9.140625" style="5"/>
+    <col min="31" max="31" width="20.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="153" style="5" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="19.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="8.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -973,88 +1007,112 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AH1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AN1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AR1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N2" s="3">
         <v>20</v>
       </c>
       <c r="O2" s="3"/>
       <c r="P2" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q2" s="3">
         <v>2</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T2" s="3">
         <v>1</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -1073,56 +1131,57 @@
       <c r="AJ2" s="3"/>
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
-    </row>
-    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM2" s="3"/>
+    </row>
+    <row r="3" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N3" s="3">
         <v>17</v>
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q3" s="3">
         <v>7</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T3" s="3">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -1141,56 +1200,57 @@
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
-    </row>
-    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM3" s="3"/>
+    </row>
+    <row r="4" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N4" s="3">
         <v>24</v>
       </c>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q4" s="3">
         <v>2</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T4" s="3">
         <v>1</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -1209,56 +1269,57 @@
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
-    </row>
-    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM4" s="3"/>
+    </row>
+    <row r="5" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N5" s="3">
         <v>21</v>
       </c>
       <c r="O5" s="3"/>
       <c r="P5" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q5" s="3">
         <v>7</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T5" s="3">
         <v>1</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -1277,56 +1338,57 @@
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
-    </row>
-    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM5" s="3"/>
+    </row>
+    <row r="6" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N6" s="3">
         <v>30</v>
       </c>
       <c r="O6" s="3"/>
       <c r="P6" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q6" s="3">
         <v>2</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T6" s="3">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -1345,56 +1407,57 @@
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
-    </row>
-    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM6" s="3"/>
+    </row>
+    <row r="7" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N7" s="3">
         <v>27</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q7" s="3">
         <v>7</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T7" s="3">
         <v>1</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
@@ -1413,58 +1476,59 @@
       <c r="AJ7" s="3"/>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
-    </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM7" s="3"/>
+    </row>
+    <row r="8" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N8" s="3">
         <v>6</v>
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>1</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="T8" s="3">
+        <v>1</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>1</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="T8" s="3">
-        <v>1</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
@@ -1483,58 +1547,59 @@
       <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
-    </row>
-    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM8" s="3"/>
+    </row>
+    <row r="9" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N9" s="3">
         <v>6</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>1</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="T9" s="3">
+        <v>1</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>1</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="T9" s="3">
-        <v>1</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
@@ -1553,58 +1618,59 @@
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
-    </row>
-    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM9" s="3"/>
+    </row>
+    <row r="10" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N10" s="3">
         <v>5</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="T10" s="3">
+        <v>1</v>
+      </c>
+      <c r="U10" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>1</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
@@ -1623,56 +1689,57 @@
       <c r="AJ10" s="3"/>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
-    </row>
-    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM10" s="3"/>
+    </row>
+    <row r="11" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q11" s="3">
         <v>1</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T11" s="3">
         <v>1</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
@@ -1684,77 +1751,75 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AF11" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG11" s="3">
+        <v>129</v>
+      </c>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3">
         <v>1.1366719999999999</v>
       </c>
-      <c r="AH11" s="3">
+      <c r="AJ11" s="3">
         <v>4.1838E-2</v>
       </c>
-      <c r="AI11" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ11" s="3">
+      <c r="AK11" s="3">
         <v>0.97889999999999999</v>
       </c>
-      <c r="AK11" s="3">
+      <c r="AL11" s="3">
         <v>-3.8660000000000001</v>
       </c>
-      <c r="AL11" s="3"/>
-    </row>
-    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q12" s="3">
         <v>30</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T12" s="3">
         <v>1</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
@@ -1766,77 +1831,75 @@
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AF12" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="AG12" s="3">
+        <v>130</v>
+      </c>
+      <c r="AG12" s="3"/>
+      <c r="AH12" s="3"/>
+      <c r="AI12" s="3">
         <v>1.101672</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>4.1838E-2</v>
       </c>
-      <c r="AI12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>0.79769999999999996</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>-3.9089999999999998</v>
       </c>
-      <c r="AL12" s="3"/>
-    </row>
-    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E13" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q13" s="3">
         <v>1</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T13" s="3">
         <v>1</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
@@ -1848,73 +1911,73 @@
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AF13" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AG13" s="3"/>
       <c r="AH13" s="3"/>
-      <c r="AI13" s="3">
+      <c r="AI13" s="3"/>
+      <c r="AJ13" s="3">
         <v>0.316</v>
       </c>
-      <c r="AJ13" s="3">
+      <c r="AK13" s="3">
         <v>0.81899999999999995</v>
       </c>
-      <c r="AK13" s="3">
+      <c r="AL13" s="3">
         <v>3.7256</v>
       </c>
-      <c r="AL13" s="3"/>
-    </row>
-    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E14" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q14" s="3">
         <v>30</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T14" s="3">
         <v>1</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
@@ -1926,73 +1989,73 @@
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AF14" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AG14" s="3"/>
       <c r="AH14" s="3"/>
-      <c r="AI14" s="3">
+      <c r="AI14" s="3"/>
+      <c r="AJ14" s="3">
         <v>0.86</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>0.81899999999999995</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>0.68479999999999996</v>
       </c>
-      <c r="AL14" s="3"/>
-    </row>
-    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q15" s="3">
         <v>1</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T15" s="3">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
@@ -2004,77 +2067,75 @@
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG15" s="3">
+        <v>133</v>
+      </c>
+      <c r="AG15" s="3"/>
+      <c r="AH15" s="3"/>
+      <c r="AI15" s="3">
         <v>1.4620299999999999</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>0.14571200000000001</v>
       </c>
-      <c r="AI15" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>1.2729999999999999</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-1.46</v>
       </c>
-      <c r="AL15" s="3"/>
-    </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q16" s="3">
         <v>30</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T16" s="3">
         <v>1</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -2086,77 +2147,75 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AF16" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AG16" s="3">
+        <v>134</v>
+      </c>
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3">
         <v>1.4620299999999999</v>
       </c>
-      <c r="AH16" s="3">
+      <c r="AJ16" s="3">
         <v>0.14571200000000001</v>
       </c>
-      <c r="AI16" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ16" s="3">
+      <c r="AK16" s="3">
         <v>1.2729999999999999</v>
       </c>
-      <c r="AK16" s="3">
+      <c r="AL16" s="3">
         <v>-4.7050000000000001</v>
       </c>
-      <c r="AL16" s="3"/>
-    </row>
-    <row r="17" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q17" s="3">
         <v>1</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T17" s="3">
         <v>1</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -2168,73 +2227,73 @@
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AF17" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AG17" s="3"/>
       <c r="AH17" s="3"/>
-      <c r="AI17" s="3">
+      <c r="AI17" s="3"/>
+      <c r="AJ17" s="3">
         <v>0.998</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>0.84599999999999997</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2.2549999999999999</v>
       </c>
-      <c r="AL17" s="3"/>
-    </row>
-    <row r="18" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E18" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q18" s="3">
         <v>30</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T18" s="3">
         <v>1</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -2246,73 +2305,73 @@
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AF18" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG18" s="3"/>
       <c r="AH18" s="3"/>
-      <c r="AI18" s="3">
+      <c r="AI18" s="3"/>
+      <c r="AJ18" s="3">
         <v>0.997</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>0.84599999999999997</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>5.8400000000000001E-2</v>
       </c>
-      <c r="AL18" s="3"/>
-    </row>
-    <row r="19" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q19" s="3">
         <v>1</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T19" s="3">
         <v>1</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -2324,73 +2383,73 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AF19" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-      <c r="AI19" s="3">
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3">
         <v>0.85</v>
       </c>
-      <c r="AJ19" s="3">
+      <c r="AK19" s="3">
         <v>1.72</v>
       </c>
-      <c r="AK19" s="3">
+      <c r="AL19" s="3">
         <v>-6.59</v>
       </c>
-      <c r="AL19" s="3"/>
-    </row>
-    <row r="20" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q20" s="3">
         <v>1</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T20" s="3">
         <v>1</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -2402,73 +2461,73 @@
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AF20" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AG20" s="3"/>
       <c r="AH20" s="3"/>
-      <c r="AI20" s="3">
+      <c r="AI20" s="3"/>
+      <c r="AJ20" s="3">
         <v>0.97799999999999998</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>0.84730000000000005</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>0.88400000000000001</v>
       </c>
-      <c r="AL20" s="3"/>
-    </row>
-    <row r="21" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E21" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q21" s="3">
         <v>30</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T21" s="3">
         <v>1</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -2480,71 +2539,71 @@
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AF21" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG21" s="3"/>
       <c r="AH21" s="3"/>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3"/>
+      <c r="AJ21" s="3">
         <v>0.98599999999999999</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>0.84730000000000005</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>0.88400000000000001</v>
       </c>
-      <c r="AL21" s="3"/>
-    </row>
-    <row r="22" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E22" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q22" s="3">
         <v>1</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T22" s="3">
         <v>1</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -2556,10 +2615,10 @@
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AF22" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AG22" s="3"/>
       <c r="AH22" s="3"/>
@@ -2567,54 +2626,55 @@
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
-    </row>
-    <row r="23" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM22" s="3"/>
+    </row>
+    <row r="23" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E23" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q23" s="3">
         <v>30</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T23" s="3">
         <v>1</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -2626,10 +2686,10 @@
       <c r="AC23" s="3"/>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF23" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="AF23" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="AG23" s="3"/>
       <c r="AH23" s="3"/>
@@ -2637,56 +2697,86 @@
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
-    </row>
-    <row r="24" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM23" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AN23" s="5">
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="AO23" s="5">
+        <v>7.6879999999999997</v>
+      </c>
+      <c r="AP23" s="5">
+        <v>1.1994</v>
+      </c>
+      <c r="AQ23" s="5">
+        <v>7.6879999999999997</v>
+      </c>
+      <c r="AR23" s="5">
+        <v>0.88759999999999994</v>
+      </c>
+      <c r="AS23" s="5">
+        <v>2.1259999999999999</v>
+      </c>
+      <c r="AT23" s="5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AU23" s="5">
+        <v>20</v>
+      </c>
+      <c r="AV23" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3">
         <v>1.5</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q24" s="3">
         <v>30</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T24" s="3">
         <v>1</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -2705,56 +2795,57 @@
       <c r="AJ24" s="3"/>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
-    </row>
-    <row r="25" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM24" s="3"/>
+    </row>
+    <row r="25" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3">
         <v>3.1</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q25" s="3">
         <v>30</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T25" s="3">
         <v>1</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -2773,56 +2864,57 @@
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
-    </row>
-    <row r="26" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM25" s="3"/>
+    </row>
+    <row r="26" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3">
         <v>20000</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q26" s="3">
         <v>30</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T26" s="3">
         <v>1</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -2841,56 +2933,57 @@
       <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
-    </row>
-    <row r="27" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM26" s="3"/>
+    </row>
+    <row r="27" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E27" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3">
         <v>340</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q27" s="3">
         <v>1</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T27" s="3">
         <v>1</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -2909,56 +3002,57 @@
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
-    </row>
-    <row r="28" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM27" s="3"/>
+    </row>
+    <row r="28" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E28" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3">
         <v>150</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q28" s="3">
         <v>30</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T28" s="3">
         <v>1</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -2977,56 +3071,57 @@
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
-    </row>
-    <row r="29" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM28" s="3"/>
+    </row>
+    <row r="29" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E29" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3">
         <v>860000</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q29" s="3">
         <v>1</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T29" s="3">
         <v>1</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -3045,56 +3140,57 @@
       <c r="AJ29" s="3"/>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
-    </row>
-    <row r="30" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM29" s="3"/>
+    </row>
+    <row r="30" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E30" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3">
         <v>230000</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q30" s="3">
         <v>30</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T30" s="3">
         <v>1</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -3113,58 +3209,59 @@
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
-    </row>
-    <row r="31" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM30" s="3"/>
+    </row>
+    <row r="31" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="E31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3">
         <v>19</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q31" s="3">
         <v>1</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T31" s="3">
         <v>1</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -3183,58 +3280,59 @@
       <c r="AJ31" s="3"/>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
-    </row>
-    <row r="32" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM31" s="3"/>
+    </row>
+    <row r="32" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="E32" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3">
         <v>11</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q32" s="3">
         <v>30</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T32" s="3">
         <v>1</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
@@ -3253,58 +3351,59 @@
       <c r="AJ32" s="3"/>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
-    </row>
-    <row r="33" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM32" s="3"/>
+    </row>
+    <row r="33" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E33" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3">
         <v>16</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q33" s="3">
         <v>1</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T33" s="3">
         <v>1</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3323,58 +3422,59 @@
       <c r="AJ33" s="3"/>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3"/>
-    </row>
-    <row r="34" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM33" s="3"/>
+    </row>
+    <row r="34" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E34" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3">
         <v>11</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q34" s="3">
         <v>30</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T34" s="3">
         <v>1</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
@@ -3393,56 +3493,57 @@
       <c r="AJ34" s="3"/>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
-    </row>
-    <row r="35" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM34" s="3"/>
+    </row>
+    <row r="35" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E35" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3">
         <v>22</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q35" s="3">
         <v>1</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T35" s="3">
         <v>1</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -3461,56 +3562,57 @@
       <c r="AJ35" s="3"/>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
-    </row>
-    <row r="36" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM35" s="3"/>
+    </row>
+    <row r="36" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E36" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3">
         <v>5.2</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q36" s="3">
         <v>30</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T36" s="3">
         <v>1</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -3529,56 +3631,57 @@
       <c r="AJ36" s="3"/>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
-    </row>
-    <row r="37" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM36" s="3"/>
+    </row>
+    <row r="37" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E37" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3">
         <v>1000</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q37" s="3">
         <v>30</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T37" s="3">
         <v>1</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
@@ -3597,56 +3700,57 @@
       <c r="AJ37" s="3"/>
       <c r="AK37" s="3"/>
       <c r="AL37" s="3"/>
-    </row>
-    <row r="38" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM37" s="3"/>
+    </row>
+    <row r="38" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E38" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3">
         <v>1.4</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q38" s="3">
         <v>1</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T38" s="3">
         <v>1</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
@@ -3665,34 +3769,35 @@
       <c r="AJ38" s="3"/>
       <c r="AK38" s="3"/>
       <c r="AL38" s="3"/>
-    </row>
-    <row r="39" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM38" s="3"/>
+    </row>
+    <row r="39" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E39" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N39" s="3">
         <v>6.5</v>
@@ -3701,22 +3806,22 @@
         <v>9</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="Q39" s="3">
         <v>7</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T39" s="3">
         <v>1</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
@@ -3735,56 +3840,57 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
-    </row>
-    <row r="40" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM39" s="3"/>
+    </row>
+    <row r="40" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E40" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3">
         <v>2</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q40" s="3">
         <v>30</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T40" s="3">
         <v>1</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -3803,54 +3909,55 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
-    </row>
-    <row r="41" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM40" s="3"/>
+    </row>
+    <row r="41" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3">
         <v>5.6</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q41" s="3">
         <v>1</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T41" s="3">
         <v>1</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -3869,54 +3976,55 @@
       <c r="AJ41" s="3"/>
       <c r="AK41" s="3"/>
       <c r="AL41" s="3"/>
-    </row>
-    <row r="42" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM41" s="3"/>
+    </row>
+    <row r="42" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3">
         <v>640</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q42" s="3">
         <v>30</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T42" s="3">
         <v>1</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
@@ -3935,54 +4043,55 @@
       <c r="AJ42" s="3"/>
       <c r="AK42" s="3"/>
       <c r="AL42" s="3"/>
-    </row>
-    <row r="43" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM42" s="3"/>
+    </row>
+    <row r="43" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q43" s="3">
         <v>1</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T43" s="3">
         <v>1</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
@@ -4001,54 +4110,55 @@
       <c r="AJ43" s="3"/>
       <c r="AK43" s="3"/>
       <c r="AL43" s="3"/>
-    </row>
-    <row r="44" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM43" s="3"/>
+    </row>
+    <row r="44" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E44" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3">
         <v>0.14000000000000001</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q44" s="3">
         <v>30</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T44" s="3">
         <v>1</v>
       </c>
       <c r="U44" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
@@ -4067,54 +4177,55 @@
       <c r="AJ44" s="3"/>
       <c r="AK44" s="3"/>
       <c r="AL44" s="3"/>
-    </row>
-    <row r="45" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM44" s="3"/>
+    </row>
+    <row r="45" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3">
         <v>7000000</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q45" s="3">
         <v>1</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T45" s="3">
         <v>1</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
@@ -4133,54 +4244,55 @@
       <c r="AJ45" s="3"/>
       <c r="AK45" s="3"/>
       <c r="AL45" s="3"/>
-    </row>
-    <row r="46" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM45" s="3"/>
+    </row>
+    <row r="46" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3">
         <v>1000</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q46" s="3">
         <v>1</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T46" s="3">
         <v>1</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -4199,54 +4311,55 @@
       <c r="AJ46" s="3"/>
       <c r="AK46" s="3"/>
       <c r="AL46" s="3"/>
-    </row>
-    <row r="47" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM46" s="3"/>
+    </row>
+    <row r="47" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3">
         <v>1300</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q47" s="3">
         <v>1</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T47" s="3">
         <v>1</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
@@ -4265,54 +4378,55 @@
       <c r="AJ47" s="3"/>
       <c r="AK47" s="3"/>
       <c r="AL47" s="3"/>
-    </row>
-    <row r="48" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM47" s="3"/>
+    </row>
+    <row r="48" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3">
         <v>4</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q48" s="3">
         <v>1</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T48" s="3">
         <v>1</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
@@ -4331,54 +4445,55 @@
       <c r="AJ48" s="3"/>
       <c r="AK48" s="3"/>
       <c r="AL48" s="3"/>
-    </row>
-    <row r="49" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM48" s="3"/>
+    </row>
+    <row r="49" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E49" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3">
         <v>400</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q49" s="3">
         <v>30</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T49" s="3">
         <v>1</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
@@ -4397,54 +4512,55 @@
       <c r="AJ49" s="3"/>
       <c r="AK49" s="3"/>
       <c r="AL49" s="3"/>
-    </row>
-    <row r="50" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM49" s="3"/>
+    </row>
+    <row r="50" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3">
         <v>50</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q50" s="3">
         <v>1</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T50" s="3">
         <v>1</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
@@ -4463,54 +4579,55 @@
       <c r="AJ50" s="3"/>
       <c r="AK50" s="3"/>
       <c r="AL50" s="3"/>
-    </row>
-    <row r="51" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM50" s="3"/>
+    </row>
+    <row r="51" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E51" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3">
         <v>100</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q51" s="3">
         <v>30</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S51" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T51" s="3">
         <v>1</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
@@ -4529,54 +4646,55 @@
       <c r="AJ51" s="3"/>
       <c r="AK51" s="3"/>
       <c r="AL51" s="3"/>
-    </row>
-    <row r="52" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM51" s="3"/>
+    </row>
+    <row r="52" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E52" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3">
         <v>0.3</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Q52" s="3">
         <v>30</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T52" s="3">
         <v>1</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
@@ -4595,54 +4713,55 @@
       <c r="AJ52" s="3"/>
       <c r="AK52" s="3"/>
       <c r="AL52" s="3"/>
-    </row>
-    <row r="53" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM52" s="3"/>
+    </row>
+    <row r="53" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E53" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="3">
         <v>0.3</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Q53" s="3">
         <v>30</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T53" s="3">
         <v>1</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
@@ -4661,54 +4780,55 @@
       <c r="AJ53" s="3"/>
       <c r="AK53" s="3"/>
       <c r="AL53" s="3"/>
-    </row>
-    <row r="54" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM53" s="3"/>
+    </row>
+    <row r="54" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3">
         <v>610</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q54" s="3">
         <v>1</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T54" s="3">
         <v>1</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
@@ -4727,54 +4847,55 @@
       <c r="AJ54" s="3"/>
       <c r="AK54" s="3"/>
       <c r="AL54" s="3"/>
-    </row>
-    <row r="55" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM54" s="3"/>
+    </row>
+    <row r="55" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E55" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3">
         <v>4600</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q55" s="3">
         <v>30</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T55" s="3">
         <v>1</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
@@ -4793,54 +4914,55 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
-    </row>
-    <row r="56" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM55" s="3"/>
+    </row>
+    <row r="56" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="3">
         <v>10000</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q56" s="3">
         <v>1</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T56" s="3">
         <v>1</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
@@ -4859,32 +4981,33 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
-    </row>
-    <row r="57" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM56" s="3"/>
+    </row>
+    <row r="57" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N57" s="3">
         <v>5</v>
@@ -4893,22 +5016,22 @@
         <v>9</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="Q57" s="3">
         <v>1</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T57" s="3">
         <v>1</v>
       </c>
       <c r="U57" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
@@ -4927,54 +5050,55 @@
       <c r="AJ57" s="3"/>
       <c r="AK57" s="3"/>
       <c r="AL57" s="3"/>
-    </row>
-    <row r="58" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM57" s="3"/>
+    </row>
+    <row r="58" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
       <c r="M58" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N58" s="3"/>
       <c r="O58" s="3">
         <v>170</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q58" s="3">
         <v>1</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T58" s="3">
         <v>1</v>
       </c>
       <c r="U58" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
@@ -4993,54 +5117,55 @@
       <c r="AJ58" s="3"/>
       <c r="AK58" s="3"/>
       <c r="AL58" s="3"/>
-    </row>
-    <row r="59" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM58" s="3"/>
+    </row>
+    <row r="59" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E59" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
       <c r="M59" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N59" s="3"/>
       <c r="O59" s="3">
         <v>4200</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q59" s="3">
         <v>30</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T59" s="3">
         <v>1</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
@@ -5059,56 +5184,57 @@
       <c r="AJ59" s="3"/>
       <c r="AK59" s="3"/>
       <c r="AL59" s="3"/>
-    </row>
-    <row r="60" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM59" s="3"/>
+    </row>
+    <row r="60" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="3"/>
       <c r="M60" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N60" s="3"/>
       <c r="O60" s="3">
         <v>250000</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q60" s="3">
         <v>1</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T60" s="3">
         <v>1</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V60" s="3"/>
       <c r="W60" s="3"/>
@@ -5127,54 +5253,55 @@
       <c r="AJ60" s="3"/>
       <c r="AK60" s="3"/>
       <c r="AL60" s="3"/>
-    </row>
-    <row r="61" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM60" s="3"/>
+    </row>
+    <row r="61" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
       <c r="M61" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N61" s="3"/>
       <c r="O61" s="3">
         <v>7400</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q61" s="3">
         <v>1</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T61" s="3">
         <v>1</v>
       </c>
       <c r="U61" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3"/>
@@ -5193,54 +5320,55 @@
       <c r="AJ61" s="3"/>
       <c r="AK61" s="3"/>
       <c r="AL61" s="3"/>
-    </row>
-    <row r="62" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM61" s="3"/>
+    </row>
+    <row r="62" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E62" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
       <c r="M62" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N62" s="3"/>
       <c r="O62" s="3">
         <v>26000</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q62" s="3">
         <v>30</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T62" s="3">
         <v>1</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3"/>
@@ -5259,6 +5387,7 @@
       <c r="AJ62" s="3"/>
       <c r="AK62" s="3"/>
       <c r="AL62" s="3"/>
+      <c r="AM62" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/inst/extdata/southern_ute_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/southern_ute_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{74D8CFAA-70F5-488B-AAC3-231A0186786E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEEF6E05-65B8-42B6-9CF6-C7B2E0D50C6B}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{74D8CFAA-70F5-488B-AAC3-231A0186786E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3C47463-1FCD-4C9B-83D4-06019DEB0B36}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8519E9F5-E322-41EB-A2D9-94E5D3901206}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8519E9F5-E322-41EB-A2D9-94E5D3901206}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="156">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -467,9 +467,6 @@
     <t>pHDirection</t>
   </si>
   <si>
-    <t>TemperatureExtreme</t>
-  </si>
-  <si>
     <t>pH_param_9</t>
   </si>
   <si>
@@ -491,7 +488,22 @@
     <t>MaxEqMagnitude</t>
   </si>
   <si>
-    <t>Max</t>
+    <t>AmmoniaEqType</t>
+  </si>
+  <si>
+    <t>pH_param_10</t>
+  </si>
+  <si>
+    <t>pH_param_11</t>
+  </si>
+  <si>
+    <t>pH_param_12</t>
+  </si>
+  <si>
+    <t>Overall Min</t>
+  </si>
+  <si>
+    <t>Max Exponent</t>
   </si>
 </sst>
 </file>
@@ -897,22 +909,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C89350-85A2-44F8-BF86-837CAD77A8FE}">
-  <dimension ref="A1:AX62"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BA62"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="9.140625" style="5"/>
-    <col min="4" max="4" width="31.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="30" width="9.140625" style="5"/>
-    <col min="31" max="31" width="20.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="9.109375" style="5"/>
+    <col min="4" max="4" width="31.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="30" width="9.109375" style="5"/>
+    <col min="31" max="31" width="20.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="153" style="5" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="19.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="8.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="5"/>
+    <col min="33" max="33" width="13.5546875" style="5" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="12.6640625" style="5" hidden="1" customWidth="1"/>
+    <col min="35" max="36" width="19.6640625" style="5" hidden="1" customWidth="1"/>
+    <col min="37" max="38" width="8.88671875" style="5" hidden="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1028,7 +1040,7 @@
         <v>34</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>35</v>
@@ -1043,28 +1055,37 @@
         <v>38</v>
       </c>
       <c r="AR1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AS1" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="AW1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="AX1" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="2" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>39</v>
@@ -1133,7 +1154,7 @@
       <c r="AL2" s="3"/>
       <c r="AM2" s="3"/>
     </row>
-    <row r="3" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -1202,7 +1223,7 @@
       <c r="AL3" s="3"/>
       <c r="AM3" s="3"/>
     </row>
-    <row r="4" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>39</v>
@@ -1271,7 +1292,7 @@
       <c r="AL4" s="3"/>
       <c r="AM4" s="3"/>
     </row>
-    <row r="5" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>39</v>
@@ -1340,7 +1361,7 @@
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
     </row>
-    <row r="6" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -1409,7 +1430,7 @@
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
     </row>
-    <row r="7" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>39</v>
@@ -1478,7 +1499,7 @@
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
     </row>
-    <row r="8" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>39</v>
@@ -1549,7 +1570,7 @@
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
     </row>
-    <row r="9" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>39</v>
@@ -1620,7 +1641,7 @@
       <c r="AL9" s="3"/>
       <c r="AM9" s="3"/>
     </row>
-    <row r="10" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>39</v>
@@ -1691,7 +1712,7 @@
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
     </row>
-    <row r="11" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>39</v>
@@ -1771,7 +1792,7 @@
         <v>-3.8660000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>39</v>
@@ -1851,7 +1872,7 @@
         <v>-3.9089999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -1929,7 +1950,7 @@
         <v>3.7256</v>
       </c>
     </row>
-    <row r="14" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>39</v>
@@ -2007,7 +2028,7 @@
         <v>0.68479999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>39</v>
@@ -2087,7 +2108,7 @@
         <v>-1.46</v>
       </c>
     </row>
-    <row r="16" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>39</v>
@@ -2167,7 +2188,7 @@
         <v>-4.7050000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -2245,7 +2266,7 @@
         <v>2.2549999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -2323,7 +2344,7 @@
         <v>5.8400000000000001E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -2401,7 +2422,7 @@
         <v>-6.59</v>
       </c>
     </row>
-    <row r="20" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>39</v>
@@ -2479,7 +2500,7 @@
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -2557,7 +2578,7 @@
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -2626,9 +2647,47 @@
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
-      <c r="AM22" s="3"/>
-    </row>
-    <row r="23" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM22" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="AN22" s="5">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="AO22" s="5">
+        <v>7.2039999999999997</v>
+      </c>
+      <c r="AP22" s="5">
+        <v>39</v>
+      </c>
+      <c r="AQ22" s="5">
+        <v>7.2039999999999997</v>
+      </c>
+      <c r="AR22" s="5">
+        <v>0.72489999999999999</v>
+      </c>
+      <c r="AS22" s="5">
+        <v>1.14E-2</v>
+      </c>
+      <c r="AT22" s="5">
+        <v>7.2039999999999997</v>
+      </c>
+      <c r="AU22" s="5">
+        <v>1.6181000000000001</v>
+      </c>
+      <c r="AV22" s="5">
+        <v>7.2039999999999997</v>
+      </c>
+      <c r="AW22" s="5">
+        <v>23.12</v>
+      </c>
+      <c r="AX22" s="5">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="AY22" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>39</v>
@@ -2698,7 +2757,7 @@
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
       <c r="AM23" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="AN23" s="5">
         <v>2.7799999999999998E-2</v>
@@ -2728,7 +2787,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -2797,7 +2856,7 @@
       <c r="AL24" s="3"/>
       <c r="AM24" s="3"/>
     </row>
-    <row r="25" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -2866,7 +2925,7 @@
       <c r="AL25" s="3"/>
       <c r="AM25" s="3"/>
     </row>
-    <row r="26" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -2935,7 +2994,7 @@
       <c r="AL26" s="3"/>
       <c r="AM26" s="3"/>
     </row>
-    <row r="27" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -3004,7 +3063,7 @@
       <c r="AL27" s="3"/>
       <c r="AM27" s="3"/>
     </row>
-    <row r="28" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>39</v>
@@ -3073,7 +3132,7 @@
       <c r="AL28" s="3"/>
       <c r="AM28" s="3"/>
     </row>
-    <row r="29" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>39</v>
@@ -3142,7 +3201,7 @@
       <c r="AL29" s="3"/>
       <c r="AM29" s="3"/>
     </row>
-    <row r="30" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>39</v>
@@ -3211,7 +3270,7 @@
       <c r="AL30" s="3"/>
       <c r="AM30" s="3"/>
     </row>
-    <row r="31" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>39</v>
@@ -3282,7 +3341,7 @@
       <c r="AL31" s="3"/>
       <c r="AM31" s="3"/>
     </row>
-    <row r="32" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>39</v>
@@ -3353,7 +3412,7 @@
       <c r="AL32" s="3"/>
       <c r="AM32" s="3"/>
     </row>
-    <row r="33" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>39</v>
@@ -3424,7 +3483,7 @@
       <c r="AL33" s="3"/>
       <c r="AM33" s="3"/>
     </row>
-    <row r="34" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>39</v>
@@ -3495,7 +3554,7 @@
       <c r="AL34" s="3"/>
       <c r="AM34" s="3"/>
     </row>
-    <row r="35" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>39</v>
@@ -3564,7 +3623,7 @@
       <c r="AL35" s="3"/>
       <c r="AM35" s="3"/>
     </row>
-    <row r="36" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>39</v>
@@ -3633,7 +3692,7 @@
       <c r="AL36" s="3"/>
       <c r="AM36" s="3"/>
     </row>
-    <row r="37" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>39</v>
@@ -3702,7 +3761,7 @@
       <c r="AL37" s="3"/>
       <c r="AM37" s="3"/>
     </row>
-    <row r="38" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
         <v>39</v>
@@ -3771,7 +3830,7 @@
       <c r="AL38" s="3"/>
       <c r="AM38" s="3"/>
     </row>
-    <row r="39" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>39</v>
@@ -3842,7 +3901,7 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
         <v>39</v>
@@ -3911,7 +3970,7 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>39</v>
@@ -3978,7 +4037,7 @@
       <c r="AL41" s="3"/>
       <c r="AM41" s="3"/>
     </row>
-    <row r="42" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>39</v>
@@ -4045,7 +4104,7 @@
       <c r="AL42" s="3"/>
       <c r="AM42" s="3"/>
     </row>
-    <row r="43" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>39</v>
@@ -4112,7 +4171,7 @@
       <c r="AL43" s="3"/>
       <c r="AM43" s="3"/>
     </row>
-    <row r="44" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
         <v>39</v>
@@ -4179,7 +4238,7 @@
       <c r="AL44" s="3"/>
       <c r="AM44" s="3"/>
     </row>
-    <row r="45" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>39</v>
@@ -4246,7 +4305,7 @@
       <c r="AL45" s="3"/>
       <c r="AM45" s="3"/>
     </row>
-    <row r="46" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
         <v>39</v>
@@ -4313,7 +4372,7 @@
       <c r="AL46" s="3"/>
       <c r="AM46" s="3"/>
     </row>
-    <row r="47" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>39</v>
@@ -4380,7 +4439,7 @@
       <c r="AL47" s="3"/>
       <c r="AM47" s="3"/>
     </row>
-    <row r="48" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
         <v>39</v>
@@ -4447,7 +4506,7 @@
       <c r="AL48" s="3"/>
       <c r="AM48" s="3"/>
     </row>
-    <row r="49" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
         <v>39</v>
@@ -4514,7 +4573,7 @@
       <c r="AL49" s="3"/>
       <c r="AM49" s="3"/>
     </row>
-    <row r="50" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
         <v>39</v>
@@ -4581,7 +4640,7 @@
       <c r="AL50" s="3"/>
       <c r="AM50" s="3"/>
     </row>
-    <row r="51" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
         <v>39</v>
@@ -4648,7 +4707,7 @@
       <c r="AL51" s="3"/>
       <c r="AM51" s="3"/>
     </row>
-    <row r="52" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
         <v>39</v>
@@ -4715,7 +4774,7 @@
       <c r="AL52" s="3"/>
       <c r="AM52" s="3"/>
     </row>
-    <row r="53" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
         <v>39</v>
@@ -4782,7 +4841,7 @@
       <c r="AL53" s="3"/>
       <c r="AM53" s="3"/>
     </row>
-    <row r="54" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
         <v>39</v>
@@ -4849,7 +4908,7 @@
       <c r="AL54" s="3"/>
       <c r="AM54" s="3"/>
     </row>
-    <row r="55" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
         <v>39</v>
@@ -4916,7 +4975,7 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
         <v>39</v>
@@ -4983,7 +5042,7 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
         <v>39</v>
@@ -5052,7 +5111,7 @@
       <c r="AL57" s="3"/>
       <c r="AM57" s="3"/>
     </row>
-    <row r="58" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
         <v>39</v>
@@ -5119,7 +5178,7 @@
       <c r="AL58" s="3"/>
       <c r="AM58" s="3"/>
     </row>
-    <row r="59" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
         <v>39</v>
@@ -5186,7 +5245,7 @@
       <c r="AL59" s="3"/>
       <c r="AM59" s="3"/>
     </row>
-    <row r="60" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
         <v>39</v>
@@ -5255,7 +5314,7 @@
       <c r="AL60" s="3"/>
       <c r="AM60" s="3"/>
     </row>
-    <row r="61" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
         <v>39</v>
@@ -5322,7 +5381,7 @@
       <c r="AL61" s="3"/>
       <c r="AM61" s="3"/>
     </row>
-    <row r="62" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
         <v>39</v>

--- a/inst/extdata/southern_ute_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/southern_ute_tribe_criteria_crosswalk.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{74D8CFAA-70F5-488B-AAC3-231A0186786E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3C47463-1FCD-4C9B-83D4-06019DEB0B36}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{74D8CFAA-70F5-488B-AAC3-231A0186786E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E48FDD0B-CBB7-45B6-B544-A611D4F1097A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8519E9F5-E322-41EB-A2D9-94E5D3901206}"/>
   </bookViews>
@@ -101,18 +101,12 @@
     <t>FreqMethod</t>
   </si>
   <si>
-    <t>AssessPeriod</t>
-  </si>
-  <si>
     <t>AssessPeriodStartDate</t>
   </si>
   <si>
     <t>AssessPeriodEndDate</t>
   </si>
   <si>
-    <t>Season</t>
-  </si>
-  <si>
     <t>SeasonStartDate</t>
   </si>
   <si>
@@ -504,6 +498,12 @@
   </si>
   <si>
     <t>Max Exponent</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Links</t>
   </si>
 </sst>
 </file>
@@ -1010,137 +1010,137 @@
         <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AI1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="AV1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="AH1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AX1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="AN1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="BA1" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N2" s="3">
         <v>20</v>
       </c>
       <c r="O2" s="3"/>
       <c r="P2" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q2" s="3">
         <v>2</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T2" s="3">
         <v>1</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
       <c r="AC2" s="3"/>
       <c r="AD2" s="3"/>
@@ -1157,59 +1157,59 @@
     <row r="3" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N3" s="3">
         <v>17</v>
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q3" s="3">
         <v>7</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T3" s="3">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
@@ -1226,59 +1226,59 @@
     <row r="4" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N4" s="3">
         <v>24</v>
       </c>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q4" s="3">
         <v>2</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T4" s="3">
         <v>1</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
@@ -1295,59 +1295,59 @@
     <row r="5" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N5" s="3">
         <v>21</v>
       </c>
       <c r="O5" s="3"/>
       <c r="P5" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q5" s="3">
         <v>7</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T5" s="3">
         <v>1</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
@@ -1364,59 +1364,59 @@
     <row r="6" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N6" s="3">
         <v>30</v>
       </c>
       <c r="O6" s="3"/>
       <c r="P6" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q6" s="3">
         <v>2</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T6" s="3">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
@@ -1433,59 +1433,59 @@
     <row r="7" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N7" s="3">
         <v>27</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q7" s="3">
         <v>7</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T7" s="3">
         <v>1</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="4"/>
-      <c r="AA7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
@@ -1502,61 +1502,61 @@
     <row r="8" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N8" s="3">
         <v>6</v>
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>1</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T8" s="3">
+        <v>1</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>1</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T8" s="3">
-        <v>1</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
@@ -1573,61 +1573,61 @@
     <row r="9" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N9" s="3">
         <v>6</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>1</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T9" s="3">
+        <v>1</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>1</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T9" s="3">
-        <v>1</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
@@ -1644,61 +1644,61 @@
     <row r="10" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N10" s="3">
         <v>5</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T10" s="3">
+        <v>1</v>
+      </c>
+      <c r="U10" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>1</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="4"/>
-      <c r="AA10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -1715,67 +1715,67 @@
     <row r="11" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q11" s="3">
         <v>1</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T11" s="3">
         <v>1</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AF11" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
@@ -1795,67 +1795,67 @@
     <row r="12" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q12" s="3">
         <v>30</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T12" s="3">
         <v>1</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AF12" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AG12" s="3"/>
       <c r="AH12" s="3"/>
@@ -1875,67 +1875,67 @@
     <row r="13" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E13" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q13" s="3">
         <v>1</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T13" s="3">
         <v>1</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="4"/>
-      <c r="AA13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AF13" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AG13" s="3"/>
       <c r="AH13" s="3"/>
@@ -1953,67 +1953,67 @@
     <row r="14" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E14" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q14" s="3">
         <v>30</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T14" s="3">
         <v>1</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="4"/>
+      <c r="X14" s="4"/>
+      <c r="Y14" s="4"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AF14" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AG14" s="3"/>
       <c r="AH14" s="3"/>
@@ -2031,67 +2031,67 @@
     <row r="15" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q15" s="3">
         <v>1</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T15" s="3">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="4"/>
-      <c r="AA15" s="4"/>
+      <c r="X15" s="4"/>
+      <c r="Y15" s="4"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AG15" s="3"/>
       <c r="AH15" s="3"/>
@@ -2111,67 +2111,67 @@
     <row r="16" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q16" s="3">
         <v>30</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T16" s="3">
         <v>1</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="4"/>
-      <c r="AA16" s="4"/>
+      <c r="X16" s="4"/>
+      <c r="Y16" s="4"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AF16" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
@@ -2191,67 +2191,67 @@
     <row r="17" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q17" s="3">
         <v>1</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T17" s="3">
         <v>1</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="4"/>
-      <c r="AA17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AF17" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AG17" s="3"/>
       <c r="AH17" s="3"/>
@@ -2269,67 +2269,67 @@
     <row r="18" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E18" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q18" s="3">
         <v>30</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T18" s="3">
         <v>1</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="4"/>
-      <c r="AA18" s="4"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AF18" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AG18" s="3"/>
       <c r="AH18" s="3"/>
@@ -2347,67 +2347,67 @@
     <row r="19" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q19" s="3">
         <v>1</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T19" s="3">
         <v>1</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AF19" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
@@ -2425,67 +2425,67 @@
     <row r="20" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q20" s="3">
         <v>1</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T20" s="3">
         <v>1</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="4"/>
-      <c r="AA20" s="4"/>
+      <c r="X20" s="4"/>
+      <c r="Y20" s="4"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AF20" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG20" s="3"/>
       <c r="AH20" s="3"/>
@@ -2503,67 +2503,67 @@
     <row r="21" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E21" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q21" s="3">
         <v>30</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T21" s="3">
         <v>1</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="4"/>
-      <c r="AA21" s="4"/>
+      <c r="X21" s="4"/>
+      <c r="Y21" s="4"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
       <c r="AB21" s="3"/>
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AF21" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG21" s="3"/>
       <c r="AH21" s="3"/>
@@ -2581,65 +2581,65 @@
     <row r="22" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E22" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q22" s="3">
         <v>1</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T22" s="3">
         <v>1</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="4"/>
-      <c r="AA22" s="4"/>
+      <c r="X22" s="4"/>
+      <c r="Y22" s="4"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
       <c r="AB22" s="3"/>
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AF22" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AG22" s="3"/>
       <c r="AH22" s="3"/>
@@ -2648,7 +2648,7 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
       <c r="AM22" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AN22" s="5">
         <v>0.27500000000000002</v>
@@ -2690,65 +2690,65 @@
     <row r="23" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E23" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q23" s="3">
         <v>30</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T23" s="3">
         <v>1</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="4"/>
-      <c r="AA23" s="4"/>
+      <c r="X23" s="4"/>
+      <c r="Y23" s="4"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
       <c r="AB23" s="3"/>
       <c r="AC23" s="3"/>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF23" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="AF23" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="AG23" s="3"/>
       <c r="AH23" s="3"/>
@@ -2757,7 +2757,7 @@
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
       <c r="AM23" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AN23" s="5">
         <v>2.7799999999999998E-2</v>
@@ -2790,59 +2790,59 @@
     <row r="24" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3">
         <v>1.5</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q24" s="3">
         <v>30</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T24" s="3">
         <v>1</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="4"/>
-      <c r="AA24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
       <c r="AB24" s="3"/>
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
@@ -2859,59 +2859,59 @@
     <row r="25" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3">
         <v>3.1</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q25" s="3">
         <v>30</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T25" s="3">
         <v>1</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="4"/>
-      <c r="AA25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
       <c r="AB25" s="3"/>
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
@@ -2928,59 +2928,59 @@
     <row r="26" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3">
         <v>20000</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q26" s="3">
         <v>30</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T26" s="3">
         <v>1</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-      <c r="Z26" s="4"/>
-      <c r="AA26" s="4"/>
+      <c r="X26" s="4"/>
+      <c r="Y26" s="4"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
@@ -2997,59 +2997,59 @@
     <row r="27" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E27" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3">
         <v>340</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q27" s="3">
         <v>1</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T27" s="3">
         <v>1</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="3"/>
-      <c r="Z27" s="4"/>
-      <c r="AA27" s="4"/>
+      <c r="X27" s="4"/>
+      <c r="Y27" s="4"/>
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
       <c r="AB27" s="3"/>
       <c r="AC27" s="3"/>
       <c r="AD27" s="3"/>
@@ -3066,59 +3066,59 @@
     <row r="28" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E28" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3">
         <v>150</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q28" s="3">
         <v>30</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T28" s="3">
         <v>1</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="4"/>
-      <c r="AA28" s="4"/>
+      <c r="X28" s="4"/>
+      <c r="Y28" s="4"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
       <c r="AD28" s="3"/>
@@ -3135,59 +3135,59 @@
     <row r="29" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E29" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3">
         <v>860000</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q29" s="3">
         <v>1</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T29" s="3">
         <v>1</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
-      <c r="Y29" s="3"/>
-      <c r="Z29" s="4"/>
-      <c r="AA29" s="4"/>
+      <c r="X29" s="4"/>
+      <c r="Y29" s="4"/>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
@@ -3204,59 +3204,59 @@
     <row r="30" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E30" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3">
         <v>230000</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q30" s="3">
         <v>30</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T30" s="3">
         <v>1</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
-      <c r="X30" s="3"/>
-      <c r="Y30" s="3"/>
-      <c r="Z30" s="4"/>
-      <c r="AA30" s="4"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4"/>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
       <c r="AB30" s="3"/>
       <c r="AC30" s="3"/>
       <c r="AD30" s="3"/>
@@ -3273,61 +3273,61 @@
     <row r="31" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="E31" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3">
         <v>19</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q31" s="3">
         <v>1</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T31" s="3">
         <v>1</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
-      <c r="X31" s="3"/>
-      <c r="Y31" s="3"/>
-      <c r="Z31" s="4"/>
-      <c r="AA31" s="4"/>
+      <c r="X31" s="4"/>
+      <c r="Y31" s="4"/>
+      <c r="Z31" s="3"/>
+      <c r="AA31" s="3"/>
       <c r="AB31" s="3"/>
       <c r="AC31" s="3"/>
       <c r="AD31" s="3"/>
@@ -3344,61 +3344,61 @@
     <row r="32" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="E32" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3">
         <v>11</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q32" s="3">
         <v>30</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T32" s="3">
         <v>1</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
-      <c r="Y32" s="3"/>
-      <c r="Z32" s="4"/>
-      <c r="AA32" s="4"/>
+      <c r="X32" s="4"/>
+      <c r="Y32" s="4"/>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
       <c r="AB32" s="3"/>
       <c r="AC32" s="3"/>
       <c r="AD32" s="3"/>
@@ -3415,61 +3415,61 @@
     <row r="33" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E33" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3">
         <v>16</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q33" s="3">
         <v>1</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T33" s="3">
         <v>1</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="4"/>
-      <c r="AA33" s="4"/>
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="3"/>
+      <c r="AA33" s="3"/>
       <c r="AB33" s="3"/>
       <c r="AC33" s="3"/>
       <c r="AD33" s="3"/>
@@ -3486,61 +3486,61 @@
     <row r="34" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E34" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3">
         <v>11</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q34" s="3">
         <v>30</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T34" s="3">
         <v>1</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
-      <c r="Z34" s="4"/>
-      <c r="AA34" s="4"/>
+      <c r="X34" s="4"/>
+      <c r="Y34" s="4"/>
+      <c r="Z34" s="3"/>
+      <c r="AA34" s="3"/>
       <c r="AB34" s="3"/>
       <c r="AC34" s="3"/>
       <c r="AD34" s="3"/>
@@ -3557,59 +3557,59 @@
     <row r="35" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E35" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3">
         <v>22</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q35" s="3">
         <v>1</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T35" s="3">
         <v>1</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="4"/>
-      <c r="AA35" s="4"/>
+      <c r="X35" s="4"/>
+      <c r="Y35" s="4"/>
+      <c r="Z35" s="3"/>
+      <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
       <c r="AD35" s="3"/>
@@ -3626,59 +3626,59 @@
     <row r="36" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E36" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3">
         <v>5.2</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q36" s="3">
         <v>30</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T36" s="3">
         <v>1</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
-      <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="4"/>
-      <c r="AA36" s="4"/>
+      <c r="X36" s="4"/>
+      <c r="Y36" s="4"/>
+      <c r="Z36" s="3"/>
+      <c r="AA36" s="3"/>
       <c r="AB36" s="3"/>
       <c r="AC36" s="3"/>
       <c r="AD36" s="3"/>
@@ -3695,59 +3695,59 @@
     <row r="37" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E37" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3">
         <v>1000</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q37" s="3">
         <v>30</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T37" s="3">
         <v>1</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
-      <c r="Y37" s="3"/>
-      <c r="Z37" s="4"/>
-      <c r="AA37" s="4"/>
+      <c r="X37" s="4"/>
+      <c r="Y37" s="4"/>
+      <c r="Z37" s="3"/>
+      <c r="AA37" s="3"/>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
       <c r="AD37" s="3"/>
@@ -3764,59 +3764,59 @@
     <row r="38" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E38" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3">
         <v>1.4</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q38" s="3">
         <v>1</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T38" s="3">
         <v>1</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
-      <c r="Y38" s="3"/>
-      <c r="Z38" s="4"/>
-      <c r="AA38" s="4"/>
+      <c r="X38" s="4"/>
+      <c r="Y38" s="4"/>
+      <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
       <c r="AD38" s="3"/>
@@ -3833,30 +3833,30 @@
     <row r="39" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E39" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N39" s="3">
         <v>6.5</v>
@@ -3865,29 +3865,29 @@
         <v>9</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q39" s="3">
         <v>7</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="T39" s="3">
         <v>1</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="4"/>
-      <c r="AA39" s="4"/>
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4"/>
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
@@ -3904,59 +3904,59 @@
     <row r="40" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E40" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3">
         <v>2</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q40" s="3">
         <v>30</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T40" s="3">
         <v>1</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="4"/>
-      <c r="AA40" s="4"/>
+      <c r="X40" s="4"/>
+      <c r="Y40" s="4"/>
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
@@ -3973,57 +3973,57 @@
     <row r="41" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3">
         <v>5.6</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q41" s="3">
         <v>1</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T41" s="3">
         <v>1</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="4"/>
-      <c r="AA41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
       <c r="AB41" s="3"/>
       <c r="AC41" s="3"/>
       <c r="AD41" s="3"/>
@@ -4040,57 +4040,57 @@
     <row r="42" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3">
         <v>640</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q42" s="3">
         <v>30</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T42" s="3">
         <v>1</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="4"/>
-      <c r="AA42" s="4"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="3"/>
+      <c r="AA42" s="3"/>
       <c r="AB42" s="3"/>
       <c r="AC42" s="3"/>
       <c r="AD42" s="3"/>
@@ -4107,57 +4107,57 @@
     <row r="43" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q43" s="3">
         <v>1</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T43" s="3">
         <v>1</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
-      <c r="X43" s="3"/>
-      <c r="Y43" s="3"/>
-      <c r="Z43" s="4"/>
-      <c r="AA43" s="4"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="3"/>
+      <c r="AA43" s="3"/>
       <c r="AB43" s="3"/>
       <c r="AC43" s="3"/>
       <c r="AD43" s="3"/>
@@ -4174,57 +4174,57 @@
     <row r="44" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E44" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3">
         <v>0.14000000000000001</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q44" s="3">
         <v>30</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T44" s="3">
         <v>1</v>
       </c>
       <c r="U44" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
-      <c r="Z44" s="4"/>
-      <c r="AA44" s="4"/>
+      <c r="X44" s="4"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="3"/>
+      <c r="AA44" s="3"/>
       <c r="AB44" s="3"/>
       <c r="AC44" s="3"/>
       <c r="AD44" s="3"/>
@@ -4241,57 +4241,57 @@
     <row r="45" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3">
         <v>7000000</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Q45" s="3">
         <v>1</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T45" s="3">
         <v>1</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
-      <c r="Y45" s="3"/>
-      <c r="Z45" s="4"/>
-      <c r="AA45" s="4"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="3"/>
+      <c r="AA45" s="3"/>
       <c r="AB45" s="3"/>
       <c r="AC45" s="3"/>
       <c r="AD45" s="3"/>
@@ -4308,57 +4308,57 @@
     <row r="46" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3">
         <v>1000</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q46" s="3">
         <v>1</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T46" s="3">
         <v>1</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
-      <c r="X46" s="3"/>
-      <c r="Y46" s="3"/>
-      <c r="Z46" s="4"/>
-      <c r="AA46" s="4"/>
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4"/>
+      <c r="Z46" s="3"/>
+      <c r="AA46" s="3"/>
       <c r="AB46" s="3"/>
       <c r="AC46" s="3"/>
       <c r="AD46" s="3"/>
@@ -4375,57 +4375,57 @@
     <row r="47" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3">
         <v>1300</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q47" s="3">
         <v>1</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T47" s="3">
         <v>1</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
-      <c r="Y47" s="3"/>
-      <c r="Z47" s="4"/>
-      <c r="AA47" s="4"/>
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="3"/>
+      <c r="AA47" s="3"/>
       <c r="AB47" s="3"/>
       <c r="AC47" s="3"/>
       <c r="AD47" s="3"/>
@@ -4442,57 +4442,57 @@
     <row r="48" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3">
         <v>4</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q48" s="3">
         <v>1</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T48" s="3">
         <v>1</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
-      <c r="X48" s="3"/>
-      <c r="Y48" s="3"/>
-      <c r="Z48" s="4"/>
-      <c r="AA48" s="4"/>
+      <c r="X48" s="4"/>
+      <c r="Y48" s="4"/>
+      <c r="Z48" s="3"/>
+      <c r="AA48" s="3"/>
       <c r="AB48" s="3"/>
       <c r="AC48" s="3"/>
       <c r="AD48" s="3"/>
@@ -4509,57 +4509,57 @@
     <row r="49" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E49" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3">
         <v>400</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q49" s="3">
         <v>30</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T49" s="3">
         <v>1</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
-      <c r="X49" s="3"/>
-      <c r="Y49" s="3"/>
-      <c r="Z49" s="4"/>
-      <c r="AA49" s="4"/>
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="3"/>
+      <c r="AA49" s="3"/>
       <c r="AB49" s="3"/>
       <c r="AC49" s="3"/>
       <c r="AD49" s="3"/>
@@ -4576,57 +4576,57 @@
     <row r="50" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3">
         <v>50</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q50" s="3">
         <v>1</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T50" s="3">
         <v>1</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
-      <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="4"/>
-      <c r="AA50" s="4"/>
+      <c r="X50" s="4"/>
+      <c r="Y50" s="4"/>
+      <c r="Z50" s="3"/>
+      <c r="AA50" s="3"/>
       <c r="AB50" s="3"/>
       <c r="AC50" s="3"/>
       <c r="AD50" s="3"/>
@@ -4643,57 +4643,57 @@
     <row r="51" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E51" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3">
         <v>100</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q51" s="3">
         <v>30</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S51" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T51" s="3">
         <v>1</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
-      <c r="X51" s="3"/>
-      <c r="Y51" s="3"/>
-      <c r="Z51" s="4"/>
-      <c r="AA51" s="4"/>
+      <c r="X51" s="4"/>
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="3"/>
+      <c r="AA51" s="3"/>
       <c r="AB51" s="3"/>
       <c r="AC51" s="3"/>
       <c r="AD51" s="3"/>
@@ -4710,57 +4710,57 @@
     <row r="52" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E52" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3">
         <v>0.3</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q52" s="3">
         <v>30</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T52" s="3">
         <v>1</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
-      <c r="X52" s="3"/>
-      <c r="Y52" s="3"/>
-      <c r="Z52" s="4"/>
-      <c r="AA52" s="4"/>
+      <c r="X52" s="4"/>
+      <c r="Y52" s="4"/>
+      <c r="Z52" s="3"/>
+      <c r="AA52" s="3"/>
       <c r="AB52" s="3"/>
       <c r="AC52" s="3"/>
       <c r="AD52" s="3"/>
@@ -4777,57 +4777,57 @@
     <row r="53" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E53" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="3">
         <v>0.3</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q53" s="3">
         <v>30</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T53" s="3">
         <v>1</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
-      <c r="X53" s="3"/>
-      <c r="Y53" s="3"/>
-      <c r="Z53" s="4"/>
-      <c r="AA53" s="4"/>
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="3"/>
+      <c r="AA53" s="3"/>
       <c r="AB53" s="3"/>
       <c r="AC53" s="3"/>
       <c r="AD53" s="3"/>
@@ -4844,57 +4844,57 @@
     <row r="54" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3">
         <v>610</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q54" s="3">
         <v>1</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T54" s="3">
         <v>1</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
-      <c r="X54" s="3"/>
-      <c r="Y54" s="3"/>
-      <c r="Z54" s="4"/>
-      <c r="AA54" s="4"/>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="3"/>
+      <c r="AA54" s="3"/>
       <c r="AB54" s="3"/>
       <c r="AC54" s="3"/>
       <c r="AD54" s="3"/>
@@ -4911,57 +4911,57 @@
     <row r="55" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E55" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3">
         <v>4600</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q55" s="3">
         <v>30</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T55" s="3">
         <v>1</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-      <c r="X55" s="3"/>
-      <c r="Y55" s="3"/>
-      <c r="Z55" s="4"/>
-      <c r="AA55" s="4"/>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
@@ -4978,57 +4978,57 @@
     <row r="56" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="3">
         <v>10000</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q56" s="3">
         <v>1</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T56" s="3">
         <v>1</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-      <c r="X56" s="3"/>
-      <c r="Y56" s="3"/>
-      <c r="Z56" s="4"/>
-      <c r="AA56" s="4"/>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
@@ -5045,28 +5045,28 @@
     <row r="57" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N57" s="3">
         <v>5</v>
@@ -5075,29 +5075,29 @@
         <v>9</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q57" s="3">
         <v>1</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="T57" s="3">
         <v>1</v>
       </c>
       <c r="U57" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
-      <c r="X57" s="3"/>
-      <c r="Y57" s="3"/>
-      <c r="Z57" s="4"/>
-      <c r="AA57" s="4"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="3"/>
+      <c r="AA57" s="3"/>
       <c r="AB57" s="3"/>
       <c r="AC57" s="3"/>
       <c r="AD57" s="3"/>
@@ -5114,57 +5114,57 @@
     <row r="58" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
       <c r="M58" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N58" s="3"/>
       <c r="O58" s="3">
         <v>170</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q58" s="3">
         <v>1</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T58" s="3">
         <v>1</v>
       </c>
       <c r="U58" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
-      <c r="X58" s="3"/>
-      <c r="Y58" s="3"/>
-      <c r="Z58" s="4"/>
-      <c r="AA58" s="4"/>
+      <c r="X58" s="4"/>
+      <c r="Y58" s="4"/>
+      <c r="Z58" s="3"/>
+      <c r="AA58" s="3"/>
       <c r="AB58" s="3"/>
       <c r="AC58" s="3"/>
       <c r="AD58" s="3"/>
@@ -5181,57 +5181,57 @@
     <row r="59" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E59" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
       <c r="M59" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N59" s="3"/>
       <c r="O59" s="3">
         <v>4200</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q59" s="3">
         <v>30</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T59" s="3">
         <v>1</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
-      <c r="X59" s="3"/>
-      <c r="Y59" s="3"/>
-      <c r="Z59" s="4"/>
-      <c r="AA59" s="4"/>
+      <c r="X59" s="4"/>
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="3"/>
+      <c r="AA59" s="3"/>
       <c r="AB59" s="3"/>
       <c r="AC59" s="3"/>
       <c r="AD59" s="3"/>
@@ -5248,59 +5248,59 @@
     <row r="60" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="3"/>
       <c r="M60" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N60" s="3"/>
       <c r="O60" s="3">
         <v>250000</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q60" s="3">
         <v>1</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T60" s="3">
         <v>1</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V60" s="3"/>
       <c r="W60" s="3"/>
-      <c r="X60" s="3"/>
-      <c r="Y60" s="3"/>
-      <c r="Z60" s="4"/>
-      <c r="AA60" s="4"/>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="3"/>
+      <c r="AA60" s="3"/>
       <c r="AB60" s="3"/>
       <c r="AC60" s="3"/>
       <c r="AD60" s="3"/>
@@ -5317,57 +5317,57 @@
     <row r="61" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
       <c r="M61" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N61" s="3"/>
       <c r="O61" s="3">
         <v>7400</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q61" s="3">
         <v>1</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T61" s="3">
         <v>1</v>
       </c>
       <c r="U61" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3"/>
-      <c r="X61" s="3"/>
-      <c r="Y61" s="3"/>
-      <c r="Z61" s="4"/>
-      <c r="AA61" s="4"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="3"/>
       <c r="AB61" s="3"/>
       <c r="AC61" s="3"/>
       <c r="AD61" s="3"/>
@@ -5384,57 +5384,57 @@
     <row r="62" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E62" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
       <c r="M62" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N62" s="3"/>
       <c r="O62" s="3">
         <v>26000</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q62" s="3">
         <v>30</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T62" s="3">
         <v>1</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3"/>
-      <c r="X62" s="3"/>
-      <c r="Y62" s="3"/>
-      <c r="Z62" s="4"/>
-      <c r="AA62" s="4"/>
+      <c r="X62" s="4"/>
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="3"/>
+      <c r="AA62" s="3"/>
       <c r="AB62" s="3"/>
       <c r="AC62" s="3"/>
       <c r="AD62" s="3"/>
